--- a/export (12).xlsx
+++ b/export (12).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\n203253\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cargillonline-my.sharepoint.com/personal/narcisoavelino_ermitadeoliveira_cargill_com/Documents/Documents/workspace/Ravis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{720EF8A0-7AB8-4C5F-AC42-86269E1ABDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{720EF8A0-7AB8-4C5F-AC42-86269E1ABDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78072997-1F12-45BC-9181-0BDCAB6FD109}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AE70652-7B67-4E07-A6B8-91F00A094CEB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2AE70652-7B67-4E07-A6B8-91F00A094CEB}"/>
   </bookViews>
   <sheets>
     <sheet name="export (12)" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="194">
   <si>
     <t>Natureza</t>
   </si>
@@ -374,6 +374,234 @@
   </si>
   <si>
     <t>conta da embasa de fevereiro que eu paguei errado</t>
+  </si>
+  <si>
+    <t>09004212000111 - QUALY DISTRIBUICAO DE ARMAZENAGEM E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>DIARIAS Taina</t>
+  </si>
+  <si>
+    <t>Salario aryellen</t>
+  </si>
+  <si>
+    <t>Salario Evelyn</t>
+  </si>
+  <si>
+    <t>00. Outros</t>
+  </si>
+  <si>
+    <t>OUTROS</t>
+  </si>
+  <si>
+    <t>cartao andressa mercado livre</t>
+  </si>
+  <si>
+    <t>TESOURA PARA BANDANA</t>
+  </si>
+  <si>
+    <t>5. Despesas Bancarias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maquina da infynit pay </t>
+  </si>
+  <si>
+    <t>99. Despesas com aderecos banho e tosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tecido bandana, adesivo </t>
+  </si>
+  <si>
+    <t>bem pratico sistema cartao Andressa</t>
+  </si>
+  <si>
+    <t>custo com a producao de videos Fernanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92. Despesas laboratorio </t>
+  </si>
+  <si>
+    <t>clinica veterinaria</t>
+  </si>
+  <si>
+    <t>120 - Itens de Consumo da Clinica</t>
+  </si>
+  <si>
+    <t>laborvet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSS - Imposto trabalhista </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSS </t>
+  </si>
+  <si>
+    <t>Imposto</t>
+  </si>
+  <si>
+    <t>FGTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93. Comissao veterinario </t>
+  </si>
+  <si>
+    <t>Comissao Veterinario Tarciana Reis</t>
+  </si>
+  <si>
+    <t>comissao - incluso consulta de GUS</t>
+  </si>
+  <si>
+    <t>4.1 Premiacoes</t>
+  </si>
+  <si>
+    <t>Premiacao time</t>
+  </si>
+  <si>
+    <t>Se bater todas as metas</t>
+  </si>
+  <si>
+    <t>CARTAO DE CREDITO RAVIS tinta e lona</t>
+  </si>
+  <si>
+    <t>59378303000195 - 59.378.303 LEONARDO SILVA COUTINHO DE JESUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narciso planilhas </t>
+  </si>
+  <si>
+    <t>Simples nacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilson - lacos </t>
+  </si>
+  <si>
+    <t>210 - Adiantamento de Salario</t>
+  </si>
+  <si>
+    <t>adiantamento karine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">conta da vivo em atraso </t>
+  </si>
+  <si>
+    <t>Pro labore</t>
+  </si>
+  <si>
+    <t>Venda ao Consumidor</t>
+  </si>
+  <si>
+    <t>Estornado pelo cancelamento da venda #5705</t>
+  </si>
+  <si>
+    <t>42407468000145 - FTFSA REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>salario karine</t>
+  </si>
+  <si>
+    <t>salario thaina</t>
+  </si>
+  <si>
+    <t>Presente</t>
+  </si>
+  <si>
+    <t>gratificacao</t>
+  </si>
+  <si>
+    <t>Cartao de credito</t>
+  </si>
+  <si>
+    <t>CARTAO DE CREDITO RAVIS</t>
+  </si>
+  <si>
+    <t>8. Compra de insumos clinica</t>
+  </si>
+  <si>
+    <t>ferias evelyn</t>
+  </si>
+  <si>
+    <t>transporte</t>
+  </si>
+  <si>
+    <t>porta de vidro</t>
+  </si>
+  <si>
+    <t>fernanda mkt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passagem bia </t>
+  </si>
+  <si>
+    <t>Corrida 99 para cinthia</t>
+  </si>
+  <si>
+    <t>Beto</t>
+  </si>
+  <si>
+    <t>Moto Boy Francis</t>
+  </si>
+  <si>
+    <t>200 - Comissao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comissao tarciana </t>
+  </si>
+  <si>
+    <t>05853741000139 - CONCORD DISTRIBUIDORA DE ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>diaria alam</t>
+  </si>
+  <si>
+    <t>teste admissional Beatriz</t>
+  </si>
+  <si>
+    <t>agua mineral</t>
+  </si>
+  <si>
+    <t>decoracao de sao joao e insumos banho e tosa</t>
+  </si>
+  <si>
+    <t>ICMS</t>
+  </si>
+  <si>
+    <t>EXAME ADMISSIONAL O OUTRO FOI DEMISSIONAL DA ARY</t>
+  </si>
+  <si>
+    <t>Adiantamento de salario karine</t>
+  </si>
+  <si>
+    <t>embasa</t>
+  </si>
+  <si>
+    <t>beto porta de vidro</t>
+  </si>
+  <si>
+    <t>vacina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua - 2,00 para agua que ficou devendo </t>
+  </si>
+  <si>
+    <t>Investimentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean UP - ratos </t>
+  </si>
+  <si>
+    <t>iFOOD PREMIACAO</t>
+  </si>
+  <si>
+    <t>Agua mineral</t>
+  </si>
+  <si>
+    <t>Sistema</t>
+  </si>
+  <si>
+    <t>Taxas trabalhistas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimo terceiro </t>
   </si>
 </sst>
 </file>
@@ -1236,8 +1464,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74594458-4EE5-4284-B3AE-E80D18FE7B04}">
-  <dimension ref="A1:AA53"/>
+  <dimension ref="A1:AA204"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="70.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="42.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -3465,7 +3722,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -3515,7 +3772,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -3556,7 +3813,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -3606,7 +3863,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -3656,7 +3913,7 @@
         <v>46111</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -3695,9 +3952,6827 @@
       </c>
       <c r="V53" s="2">
         <v>46111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" t="s">
+        <v>36</v>
+      </c>
+      <c r="H54" t="s">
+        <v>41</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>425.54</v>
+      </c>
+      <c r="N54">
+        <v>425.54</v>
+      </c>
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="T54" s="2">
+        <v>46144</v>
+      </c>
+      <c r="U54" s="2">
+        <v>46143</v>
+      </c>
+      <c r="V54" s="2">
+        <v>46118</v>
+      </c>
+      <c r="W54" s="2">
+        <v>46144</v>
+      </c>
+      <c r="X54">
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" t="s">
+        <v>49</v>
+      </c>
+      <c r="D55" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" t="s">
+        <v>36</v>
+      </c>
+      <c r="H55" t="s">
+        <v>118</v>
+      </c>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>251.51</v>
+      </c>
+      <c r="N55">
+        <v>251.51</v>
+      </c>
+      <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="T55" s="2">
+        <v>46144</v>
+      </c>
+      <c r="U55" s="2">
+        <v>46144</v>
+      </c>
+      <c r="V55" s="2">
+        <v>46100</v>
+      </c>
+      <c r="W55" s="2">
+        <v>46144</v>
+      </c>
+      <c r="X55">
+        <v>777612</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" t="s">
+        <v>36</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>533.92999999999995</v>
+      </c>
+      <c r="N56">
+        <v>533.92999999999995</v>
+      </c>
+      <c r="O56">
+        <v>3</v>
+      </c>
+      <c r="P56">
+        <v>10</v>
+      </c>
+      <c r="R56" t="s">
+        <v>72</v>
+      </c>
+      <c r="S56" s="2">
+        <v>46111</v>
+      </c>
+      <c r="T56" s="2">
+        <v>46144</v>
+      </c>
+      <c r="U56" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V56" s="2">
+        <v>46086</v>
+      </c>
+      <c r="W56" s="2">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" t="s">
+        <v>43</v>
+      </c>
+      <c r="E57" t="s">
+        <v>36</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>507.99</v>
+      </c>
+      <c r="N57">
+        <v>458.46</v>
+      </c>
+      <c r="O57">
+        <v>5</v>
+      </c>
+      <c r="P57">
+        <v>12</v>
+      </c>
+      <c r="R57" t="s">
+        <v>79</v>
+      </c>
+      <c r="S57" s="2">
+        <v>46038</v>
+      </c>
+      <c r="T57" s="2">
+        <v>46144</v>
+      </c>
+      <c r="U57" s="2">
+        <v>46143</v>
+      </c>
+      <c r="V57" s="2">
+        <v>46023</v>
+      </c>
+      <c r="W57" s="2">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C58" t="s">
+        <v>46</v>
+      </c>
+      <c r="D58" t="s">
+        <v>58</v>
+      </c>
+      <c r="E58" t="s">
+        <v>36</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>595</v>
+      </c>
+      <c r="N58">
+        <v>595</v>
+      </c>
+      <c r="R58" t="s">
+        <v>119</v>
+      </c>
+      <c r="S58" s="2">
+        <v>46144</v>
+      </c>
+      <c r="T58" s="2">
+        <v>46144</v>
+      </c>
+      <c r="U58" s="2">
+        <v>46144</v>
+      </c>
+      <c r="V58" s="2">
+        <v>46143</v>
+      </c>
+      <c r="W58" s="2">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" t="s">
+        <v>58</v>
+      </c>
+      <c r="E59" t="s">
+        <v>36</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="M59" s="1">
+        <v>1402.17</v>
+      </c>
+      <c r="N59" s="1">
+        <v>1402.17</v>
+      </c>
+      <c r="O59">
+        <v>1</v>
+      </c>
+      <c r="P59">
+        <v>2</v>
+      </c>
+      <c r="R59" t="s">
+        <v>120</v>
+      </c>
+      <c r="S59" s="2">
+        <v>46141</v>
+      </c>
+      <c r="T59" s="2">
+        <v>46146</v>
+      </c>
+      <c r="U59" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V59" s="2">
+        <v>46147</v>
+      </c>
+      <c r="W59" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" t="s">
+        <v>58</v>
+      </c>
+      <c r="E60" t="s">
+        <v>36</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>1529.67</v>
+      </c>
+      <c r="N60" s="1">
+        <v>1529.67</v>
+      </c>
+      <c r="O60">
+        <v>2</v>
+      </c>
+      <c r="P60">
+        <v>8</v>
+      </c>
+      <c r="R60" t="s">
+        <v>121</v>
+      </c>
+      <c r="S60" s="2">
+        <v>46116</v>
+      </c>
+      <c r="T60" s="2">
+        <v>46146</v>
+      </c>
+      <c r="U60" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V60" s="2">
+        <v>46117</v>
+      </c>
+      <c r="W60" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" t="s">
+        <v>36</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>1155.17</v>
+      </c>
+      <c r="N61" s="1">
+        <v>1313.07</v>
+      </c>
+      <c r="O61">
+        <v>7</v>
+      </c>
+      <c r="P61">
+        <v>12</v>
+      </c>
+      <c r="R61" t="s">
+        <v>60</v>
+      </c>
+      <c r="S61" s="2">
+        <v>45931</v>
+      </c>
+      <c r="T61" s="2">
+        <v>46146</v>
+      </c>
+      <c r="U61" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V61" s="2">
+        <v>45966</v>
+      </c>
+      <c r="W61" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" t="s">
+        <v>36</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>216</v>
+      </c>
+      <c r="N62">
+        <v>216</v>
+      </c>
+      <c r="O62">
+        <v>14</v>
+      </c>
+      <c r="P62">
+        <v>54</v>
+      </c>
+      <c r="R62" t="s">
+        <v>48</v>
+      </c>
+      <c r="S62" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T62" s="2">
+        <v>46146</v>
+      </c>
+      <c r="U62" s="2">
+        <v>46146</v>
+      </c>
+      <c r="V62" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W62" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B63" t="s">
+        <v>42</v>
+      </c>
+      <c r="C63" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" t="s">
+        <v>61</v>
+      </c>
+      <c r="E63" t="s">
+        <v>36</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>2500</v>
+      </c>
+      <c r="N63" s="1">
+        <v>2500</v>
+      </c>
+      <c r="O63">
+        <v>4</v>
+      </c>
+      <c r="P63">
+        <v>12</v>
+      </c>
+      <c r="R63" t="s">
+        <v>62</v>
+      </c>
+      <c r="S63" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T63" s="2">
+        <v>46146</v>
+      </c>
+      <c r="U63" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V63" s="2">
+        <v>46058</v>
+      </c>
+      <c r="W63" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64" t="s">
+        <v>98</v>
+      </c>
+      <c r="E64" t="s">
+        <v>36</v>
+      </c>
+      <c r="H64" t="s">
+        <v>77</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>328.54</v>
+      </c>
+      <c r="N64">
+        <v>328.54</v>
+      </c>
+      <c r="P64">
+        <v>1</v>
+      </c>
+      <c r="T64" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U64" s="2">
+        <v>46148</v>
+      </c>
+      <c r="V64" s="2">
+        <v>46052</v>
+      </c>
+      <c r="W64" s="2">
+        <v>46147</v>
+      </c>
+      <c r="X64">
+        <v>60852</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65" t="s">
+        <v>122</v>
+      </c>
+      <c r="C65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" t="s">
+        <v>123</v>
+      </c>
+      <c r="E65" t="s">
+        <v>36</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>27.45</v>
+      </c>
+      <c r="N65">
+        <v>27.45</v>
+      </c>
+      <c r="R65" t="s">
+        <v>124</v>
+      </c>
+      <c r="S65" s="2">
+        <v>46147</v>
+      </c>
+      <c r="T65" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U65" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V65" s="2">
+        <v>46143</v>
+      </c>
+      <c r="W65" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>27</v>
+      </c>
+      <c r="B66" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" t="s">
+        <v>46</v>
+      </c>
+      <c r="D66" t="s">
+        <v>39</v>
+      </c>
+      <c r="E66" t="s">
+        <v>36</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>38.78</v>
+      </c>
+      <c r="N66">
+        <v>38.78</v>
+      </c>
+      <c r="R66" t="s">
+        <v>125</v>
+      </c>
+      <c r="S66" s="2">
+        <v>46146</v>
+      </c>
+      <c r="T66" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U66" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V66" s="2">
+        <v>46132</v>
+      </c>
+      <c r="W66" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>27</v>
+      </c>
+      <c r="B67" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" t="s">
+        <v>63</v>
+      </c>
+      <c r="E67" t="s">
+        <v>36</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>15.35</v>
+      </c>
+      <c r="N67">
+        <v>15.35</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+      <c r="P67">
+        <v>6</v>
+      </c>
+      <c r="R67" t="s">
+        <v>127</v>
+      </c>
+      <c r="S67" s="2">
+        <v>46141</v>
+      </c>
+      <c r="T67" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U67" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V67" s="2">
+        <v>46147</v>
+      </c>
+      <c r="W67" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" t="s">
+        <v>46</v>
+      </c>
+      <c r="D68" t="s">
+        <v>39</v>
+      </c>
+      <c r="E68" t="s">
+        <v>36</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>23.63</v>
+      </c>
+      <c r="N68">
+        <v>23.63</v>
+      </c>
+      <c r="O68">
+        <v>2</v>
+      </c>
+      <c r="P68">
+        <v>2</v>
+      </c>
+      <c r="R68" t="s">
+        <v>129</v>
+      </c>
+      <c r="S68" s="2">
+        <v>46116</v>
+      </c>
+      <c r="T68" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U68" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V68" s="2">
+        <v>46117</v>
+      </c>
+      <c r="W68" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>27</v>
+      </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" t="s">
+        <v>65</v>
+      </c>
+      <c r="E69" t="s">
+        <v>36</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>199.92</v>
+      </c>
+      <c r="N69">
+        <v>199.92</v>
+      </c>
+      <c r="O69">
+        <v>2</v>
+      </c>
+      <c r="P69">
+        <v>10</v>
+      </c>
+      <c r="R69" t="s">
+        <v>130</v>
+      </c>
+      <c r="S69" s="2">
+        <v>46116</v>
+      </c>
+      <c r="T69" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U69" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V69" s="2">
+        <v>46117</v>
+      </c>
+      <c r="W69" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>27</v>
+      </c>
+      <c r="B70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" t="s">
+        <v>67</v>
+      </c>
+      <c r="E70" t="s">
+        <v>36</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>799</v>
+      </c>
+      <c r="N70">
+        <v>799</v>
+      </c>
+      <c r="O70">
+        <v>6</v>
+      </c>
+      <c r="P70">
+        <v>10</v>
+      </c>
+      <c r="R70" t="s">
+        <v>68</v>
+      </c>
+      <c r="S70" s="2">
+        <v>46052</v>
+      </c>
+      <c r="T70" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U70" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V70" s="2">
+        <v>45996</v>
+      </c>
+      <c r="W70" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>27</v>
+      </c>
+      <c r="B71" t="s">
+        <v>88</v>
+      </c>
+      <c r="C71" t="s">
+        <v>46</v>
+      </c>
+      <c r="D71" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71" t="s">
+        <v>36</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>500</v>
+      </c>
+      <c r="N71">
+        <v>500</v>
+      </c>
+      <c r="R71" t="s">
+        <v>131</v>
+      </c>
+      <c r="S71" s="2">
+        <v>46147</v>
+      </c>
+      <c r="T71" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U71" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V71" s="2">
+        <v>46147</v>
+      </c>
+      <c r="W71" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" t="s">
+        <v>133</v>
+      </c>
+      <c r="D72" t="s">
+        <v>134</v>
+      </c>
+      <c r="E72" t="s">
+        <v>36</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>235</v>
+      </c>
+      <c r="N72">
+        <v>235</v>
+      </c>
+      <c r="R72" t="s">
+        <v>135</v>
+      </c>
+      <c r="S72" s="2">
+        <v>46147</v>
+      </c>
+      <c r="T72" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U72" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V72" s="2">
+        <v>46143</v>
+      </c>
+      <c r="W72" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>27</v>
+      </c>
+      <c r="B73" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73" t="s">
+        <v>98</v>
+      </c>
+      <c r="E73" t="s">
+        <v>36</v>
+      </c>
+      <c r="H73" t="s">
+        <v>118</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>251.51</v>
+      </c>
+      <c r="N73">
+        <v>251.51</v>
+      </c>
+      <c r="P73">
+        <v>1</v>
+      </c>
+      <c r="T73" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U73" s="2">
+        <v>46151</v>
+      </c>
+      <c r="V73" s="2">
+        <v>46100</v>
+      </c>
+      <c r="W73" s="2">
+        <v>46147</v>
+      </c>
+      <c r="X73">
+        <v>777612</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>27</v>
+      </c>
+      <c r="B74" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" t="s">
+        <v>136</v>
+      </c>
+      <c r="E74" t="s">
+        <v>36</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>697.21</v>
+      </c>
+      <c r="N74">
+        <v>697.21</v>
+      </c>
+      <c r="O74">
+        <v>1</v>
+      </c>
+      <c r="P74">
+        <v>8</v>
+      </c>
+      <c r="R74" t="s">
+        <v>137</v>
+      </c>
+      <c r="S74" s="2">
+        <v>46146</v>
+      </c>
+      <c r="T74" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U74" s="2">
+        <v>46162</v>
+      </c>
+      <c r="V74" s="2">
+        <v>46162</v>
+      </c>
+      <c r="W74" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>27</v>
+      </c>
+      <c r="B75" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" t="s">
+        <v>138</v>
+      </c>
+      <c r="E75" t="s">
+        <v>36</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>648.04</v>
+      </c>
+      <c r="N75">
+        <v>648.04</v>
+      </c>
+      <c r="O75">
+        <v>1</v>
+      </c>
+      <c r="P75">
+        <v>8</v>
+      </c>
+      <c r="R75" t="s">
+        <v>139</v>
+      </c>
+      <c r="S75" s="2">
+        <v>46146</v>
+      </c>
+      <c r="T75" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U75" s="2">
+        <v>46162</v>
+      </c>
+      <c r="V75" s="2">
+        <v>46162</v>
+      </c>
+      <c r="W75" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>27</v>
+      </c>
+      <c r="B76" t="s">
+        <v>140</v>
+      </c>
+      <c r="C76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D76" t="s">
+        <v>141</v>
+      </c>
+      <c r="E76" t="s">
+        <v>36</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>766.25</v>
+      </c>
+      <c r="N76">
+        <v>766.25</v>
+      </c>
+      <c r="R76" t="s">
+        <v>142</v>
+      </c>
+      <c r="S76" s="2">
+        <v>46147</v>
+      </c>
+      <c r="T76" s="2">
+        <v>46147</v>
+      </c>
+      <c r="U76" s="2">
+        <v>46147</v>
+      </c>
+      <c r="V76" s="2">
+        <v>46147</v>
+      </c>
+      <c r="W76" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>27</v>
+      </c>
+      <c r="B77" t="s">
+        <v>143</v>
+      </c>
+      <c r="C77" t="s">
+        <v>29</v>
+      </c>
+      <c r="D77" t="s">
+        <v>144</v>
+      </c>
+      <c r="E77" t="s">
+        <v>36</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>150</v>
+      </c>
+      <c r="N77">
+        <v>150</v>
+      </c>
+      <c r="O77">
+        <v>4</v>
+      </c>
+      <c r="P77">
+        <v>12</v>
+      </c>
+      <c r="R77" t="s">
+        <v>145</v>
+      </c>
+      <c r="S77" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T77" s="2">
+        <v>46153</v>
+      </c>
+      <c r="U77" s="2">
+        <v>46152</v>
+      </c>
+      <c r="V77" s="2">
+        <v>46063</v>
+      </c>
+      <c r="W77" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>27</v>
+      </c>
+      <c r="B78" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" t="s">
+        <v>36</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>144</v>
+      </c>
+      <c r="N78">
+        <v>144</v>
+      </c>
+      <c r="O78">
+        <v>2</v>
+      </c>
+      <c r="P78">
+        <v>3</v>
+      </c>
+      <c r="R78" t="s">
+        <v>146</v>
+      </c>
+      <c r="S78" s="2">
+        <v>46132</v>
+      </c>
+      <c r="T78" s="2">
+        <v>46153</v>
+      </c>
+      <c r="U78" s="2">
+        <v>46152</v>
+      </c>
+      <c r="V78" s="2">
+        <v>46122</v>
+      </c>
+      <c r="W78" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>27</v>
+      </c>
+      <c r="B79" t="s">
+        <v>38</v>
+      </c>
+      <c r="E79" t="s">
+        <v>36</v>
+      </c>
+      <c r="H79" t="s">
+        <v>41</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>302.38</v>
+      </c>
+      <c r="N79">
+        <v>302.38</v>
+      </c>
+      <c r="P79">
+        <v>1</v>
+      </c>
+      <c r="T79" s="2">
+        <v>46153</v>
+      </c>
+      <c r="U79" s="2">
+        <v>46153</v>
+      </c>
+      <c r="V79" s="2">
+        <v>46128</v>
+      </c>
+      <c r="W79" s="2">
+        <v>46153</v>
+      </c>
+      <c r="X79">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>27</v>
+      </c>
+      <c r="B80" t="s">
+        <v>49</v>
+      </c>
+      <c r="E80" t="s">
+        <v>36</v>
+      </c>
+      <c r="H80" t="s">
+        <v>147</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>349.08</v>
+      </c>
+      <c r="N80">
+        <v>349.08</v>
+      </c>
+      <c r="P80">
+        <v>1</v>
+      </c>
+      <c r="T80" s="2">
+        <v>46153</v>
+      </c>
+      <c r="U80" s="2">
+        <v>46153</v>
+      </c>
+      <c r="V80" s="2">
+        <v>46122</v>
+      </c>
+      <c r="W80" s="2">
+        <v>46153</v>
+      </c>
+      <c r="X80">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" t="s">
+        <v>49</v>
+      </c>
+      <c r="E81" t="s">
+        <v>36</v>
+      </c>
+      <c r="H81" t="s">
+        <v>51</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>225.58</v>
+      </c>
+      <c r="N81">
+        <v>225.58</v>
+      </c>
+      <c r="P81">
+        <v>1</v>
+      </c>
+      <c r="T81" s="2">
+        <v>46153</v>
+      </c>
+      <c r="U81" s="2">
+        <v>46155</v>
+      </c>
+      <c r="V81" s="2">
+        <v>46125</v>
+      </c>
+      <c r="W81" s="2">
+        <v>46153</v>
+      </c>
+      <c r="X81">
+        <v>253408</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>27</v>
+      </c>
+      <c r="B82" t="s">
+        <v>45</v>
+      </c>
+      <c r="C82" t="s">
+        <v>46</v>
+      </c>
+      <c r="D82" t="s">
+        <v>47</v>
+      </c>
+      <c r="E82" t="s">
+        <v>36</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>198</v>
+      </c>
+      <c r="N82">
+        <v>216</v>
+      </c>
+      <c r="O82">
+        <v>15</v>
+      </c>
+      <c r="P82">
+        <v>54</v>
+      </c>
+      <c r="R82" t="s">
+        <v>48</v>
+      </c>
+      <c r="S82" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T82" s="2">
+        <v>46153</v>
+      </c>
+      <c r="U82" s="2">
+        <v>46153</v>
+      </c>
+      <c r="V82" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W82" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>27</v>
+      </c>
+      <c r="B83" t="s">
+        <v>49</v>
+      </c>
+      <c r="D83" t="s">
+        <v>98</v>
+      </c>
+      <c r="E83" t="s">
+        <v>36</v>
+      </c>
+      <c r="H83" t="s">
+        <v>118</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>251.51</v>
+      </c>
+      <c r="N83">
+        <v>251.51</v>
+      </c>
+      <c r="P83">
+        <v>1</v>
+      </c>
+      <c r="T83" s="2">
+        <v>46153</v>
+      </c>
+      <c r="U83" s="2">
+        <v>46158</v>
+      </c>
+      <c r="V83" s="2">
+        <v>46100</v>
+      </c>
+      <c r="W83" s="2">
+        <v>46153</v>
+      </c>
+      <c r="X83">
+        <v>777612</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>27</v>
+      </c>
+      <c r="B84" t="s">
+        <v>42</v>
+      </c>
+      <c r="C84" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" t="s">
+        <v>80</v>
+      </c>
+      <c r="E84" t="s">
+        <v>36</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>180</v>
+      </c>
+      <c r="N84">
+        <v>180</v>
+      </c>
+      <c r="O84">
+        <v>5</v>
+      </c>
+      <c r="P84">
+        <v>12</v>
+      </c>
+      <c r="R84" t="s">
+        <v>81</v>
+      </c>
+      <c r="S84" s="2">
+        <v>46043</v>
+      </c>
+      <c r="T84" s="2">
+        <v>46153</v>
+      </c>
+      <c r="U84" s="2">
+        <v>46157</v>
+      </c>
+      <c r="V84" s="2">
+        <v>46037</v>
+      </c>
+      <c r="W84" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>27</v>
+      </c>
+      <c r="B85" t="s">
+        <v>34</v>
+      </c>
+      <c r="C85" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" t="s">
+        <v>94</v>
+      </c>
+      <c r="E85" t="s">
+        <v>36</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="M85" s="1">
+        <v>1500</v>
+      </c>
+      <c r="N85" s="1">
+        <v>1500</v>
+      </c>
+      <c r="R85" t="s">
+        <v>148</v>
+      </c>
+      <c r="S85" s="2">
+        <v>46163</v>
+      </c>
+      <c r="T85" s="2">
+        <v>46157</v>
+      </c>
+      <c r="U85" s="2">
+        <v>46157</v>
+      </c>
+      <c r="V85" s="2">
+        <v>46157</v>
+      </c>
+      <c r="W85" s="2">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>27</v>
+      </c>
+      <c r="B86" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" t="s">
+        <v>47</v>
+      </c>
+      <c r="E86" t="s">
+        <v>36</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>216</v>
+      </c>
+      <c r="N86">
+        <v>216</v>
+      </c>
+      <c r="O86">
+        <v>16</v>
+      </c>
+      <c r="P86">
+        <v>54</v>
+      </c>
+      <c r="R86" t="s">
+        <v>48</v>
+      </c>
+      <c r="S86" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T86" s="2">
+        <v>46160</v>
+      </c>
+      <c r="U86" s="2">
+        <v>46160</v>
+      </c>
+      <c r="V86" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W86" s="2">
+        <v>46160</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>27</v>
+      </c>
+      <c r="B87" t="s">
+        <v>103</v>
+      </c>
+      <c r="C87" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" t="s">
+        <v>104</v>
+      </c>
+      <c r="E87" t="s">
+        <v>36</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="M87" s="1">
+        <v>2135.9899999999998</v>
+      </c>
+      <c r="N87" s="1">
+        <v>3157.93</v>
+      </c>
+      <c r="O87">
+        <v>2</v>
+      </c>
+      <c r="P87">
+        <v>10</v>
+      </c>
+      <c r="R87" t="s">
+        <v>149</v>
+      </c>
+      <c r="S87" s="2">
+        <v>46132</v>
+      </c>
+      <c r="T87" s="2">
+        <v>46162</v>
+      </c>
+      <c r="U87" s="2">
+        <v>46162</v>
+      </c>
+      <c r="V87" s="2">
+        <v>46132</v>
+      </c>
+      <c r="W87" s="2">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B88" t="s">
+        <v>42</v>
+      </c>
+      <c r="C88" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" t="s">
+        <v>36</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>55.93</v>
+      </c>
+      <c r="N88">
+        <v>55.93</v>
+      </c>
+      <c r="O88">
+        <v>5</v>
+      </c>
+      <c r="P88">
+        <v>10</v>
+      </c>
+      <c r="R88" t="s">
+        <v>44</v>
+      </c>
+      <c r="S88" s="2">
+        <v>46032</v>
+      </c>
+      <c r="T88" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U88" s="2">
+        <v>46163</v>
+      </c>
+      <c r="V88" s="2">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>27</v>
+      </c>
+      <c r="B89" t="s">
+        <v>42</v>
+      </c>
+      <c r="D89" t="s">
+        <v>39</v>
+      </c>
+      <c r="E89" t="s">
+        <v>31</v>
+      </c>
+      <c r="F89" t="s">
+        <v>32</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>320</v>
+      </c>
+      <c r="N89">
+        <v>320</v>
+      </c>
+      <c r="R89" t="s">
+        <v>150</v>
+      </c>
+      <c r="S89" s="2">
+        <v>46163</v>
+      </c>
+      <c r="T89" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U89" s="2">
+        <v>46163</v>
+      </c>
+      <c r="V89" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>27</v>
+      </c>
+      <c r="B90" t="s">
+        <v>38</v>
+      </c>
+      <c r="D90" t="s">
+        <v>39</v>
+      </c>
+      <c r="E90" t="s">
+        <v>36</v>
+      </c>
+      <c r="H90" t="s">
+        <v>41</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="N90">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="P90">
+        <v>1</v>
+      </c>
+      <c r="T90" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U90" s="2">
+        <v>46163</v>
+      </c>
+      <c r="V90" s="2">
+        <v>46128</v>
+      </c>
+      <c r="W90" s="2">
+        <v>46163</v>
+      </c>
+      <c r="X90">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>27</v>
+      </c>
+      <c r="B91" t="s">
+        <v>34</v>
+      </c>
+      <c r="C91" t="s">
+        <v>29</v>
+      </c>
+      <c r="D91" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" t="s">
+        <v>36</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>39.770000000000003</v>
+      </c>
+      <c r="N91">
+        <v>31.41</v>
+      </c>
+      <c r="O91">
+        <v>5</v>
+      </c>
+      <c r="P91">
+        <v>12</v>
+      </c>
+      <c r="R91" t="s">
+        <v>37</v>
+      </c>
+      <c r="S91" s="2">
+        <v>46043</v>
+      </c>
+      <c r="T91" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U91" s="2">
+        <v>46157</v>
+      </c>
+      <c r="V91" s="2">
+        <v>46037</v>
+      </c>
+      <c r="W91" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>27</v>
+      </c>
+      <c r="B92" t="s">
+        <v>49</v>
+      </c>
+      <c r="D92" t="s">
+        <v>98</v>
+      </c>
+      <c r="E92" t="s">
+        <v>36</v>
+      </c>
+      <c r="H92" t="s">
+        <v>118</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>251.51</v>
+      </c>
+      <c r="N92">
+        <v>251.51</v>
+      </c>
+      <c r="P92">
+        <v>1</v>
+      </c>
+      <c r="T92" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U92" s="2">
+        <v>46165</v>
+      </c>
+      <c r="V92" s="2">
+        <v>46100</v>
+      </c>
+      <c r="W92" s="2">
+        <v>46163</v>
+      </c>
+      <c r="X92">
+        <v>777612</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>27</v>
+      </c>
+      <c r="B93" t="s">
+        <v>49</v>
+      </c>
+      <c r="D93" t="s">
+        <v>98</v>
+      </c>
+      <c r="E93" t="s">
+        <v>36</v>
+      </c>
+      <c r="H93" t="s">
+        <v>51</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>225.6</v>
+      </c>
+      <c r="N93">
+        <v>225.6</v>
+      </c>
+      <c r="P93">
+        <v>1</v>
+      </c>
+      <c r="T93" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U93" s="2">
+        <v>46165</v>
+      </c>
+      <c r="V93" s="2">
+        <v>46125</v>
+      </c>
+      <c r="W93" s="2">
+        <v>46163</v>
+      </c>
+      <c r="X93">
+        <v>253408</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>27</v>
+      </c>
+      <c r="B94" t="s">
+        <v>49</v>
+      </c>
+      <c r="D94" t="s">
+        <v>98</v>
+      </c>
+      <c r="E94" t="s">
+        <v>36</v>
+      </c>
+      <c r="H94" t="s">
+        <v>147</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>349.09</v>
+      </c>
+      <c r="N94">
+        <v>349.09</v>
+      </c>
+      <c r="P94">
+        <v>1</v>
+      </c>
+      <c r="T94" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U94" s="2">
+        <v>46168</v>
+      </c>
+      <c r="V94" s="2">
+        <v>46122</v>
+      </c>
+      <c r="W94" s="2">
+        <v>46163</v>
+      </c>
+      <c r="X94">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>27</v>
+      </c>
+      <c r="B95" t="s">
+        <v>49</v>
+      </c>
+      <c r="D95" t="s">
+        <v>98</v>
+      </c>
+      <c r="E95" t="s">
+        <v>36</v>
+      </c>
+      <c r="H95" t="s">
+        <v>118</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>251.51</v>
+      </c>
+      <c r="N95">
+        <v>251.51</v>
+      </c>
+      <c r="P95">
+        <v>1</v>
+      </c>
+      <c r="T95" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U95" s="2">
+        <v>46172</v>
+      </c>
+      <c r="V95" s="2">
+        <v>46100</v>
+      </c>
+      <c r="W95" s="2">
+        <v>46163</v>
+      </c>
+      <c r="X95">
+        <v>777612</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>27</v>
+      </c>
+      <c r="B96" t="s">
+        <v>38</v>
+      </c>
+      <c r="D96" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" t="s">
+        <v>36</v>
+      </c>
+      <c r="H96" t="s">
+        <v>41</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="N96">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="P96">
+        <v>1</v>
+      </c>
+      <c r="T96" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U96" s="2">
+        <v>46173</v>
+      </c>
+      <c r="V96" s="2">
+        <v>46128</v>
+      </c>
+      <c r="W96" s="2">
+        <v>46163</v>
+      </c>
+      <c r="X96">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>27</v>
+      </c>
+      <c r="B97" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" t="s">
+        <v>108</v>
+      </c>
+      <c r="E97" t="s">
+        <v>36</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="M97" s="1">
+        <v>1000</v>
+      </c>
+      <c r="N97" s="1">
+        <v>1000</v>
+      </c>
+      <c r="O97">
+        <v>5</v>
+      </c>
+      <c r="P97">
+        <v>12</v>
+      </c>
+      <c r="R97" t="s">
+        <v>109</v>
+      </c>
+      <c r="S97" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T97" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U97" s="2">
+        <v>46170</v>
+      </c>
+      <c r="V97" s="2">
+        <v>46052</v>
+      </c>
+      <c r="W97" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>27</v>
+      </c>
+      <c r="B98" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" t="s">
+        <v>29</v>
+      </c>
+      <c r="D98" t="s">
+        <v>108</v>
+      </c>
+      <c r="E98" t="s">
+        <v>36</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>550</v>
+      </c>
+      <c r="N98">
+        <v>550</v>
+      </c>
+      <c r="O98">
+        <v>5</v>
+      </c>
+      <c r="P98">
+        <v>12</v>
+      </c>
+      <c r="S98" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T98" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U98" s="2">
+        <v>46170</v>
+      </c>
+      <c r="V98" s="2">
+        <v>46052</v>
+      </c>
+      <c r="W98" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>27</v>
+      </c>
+      <c r="B99" t="s">
+        <v>45</v>
+      </c>
+      <c r="C99" t="s">
+        <v>89</v>
+      </c>
+      <c r="D99" t="s">
+        <v>151</v>
+      </c>
+      <c r="E99" t="s">
+        <v>36</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>250</v>
+      </c>
+      <c r="N99">
+        <v>250</v>
+      </c>
+      <c r="R99" t="s">
+        <v>152</v>
+      </c>
+      <c r="S99" s="2">
+        <v>46163</v>
+      </c>
+      <c r="T99" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U99" s="2">
+        <v>46162</v>
+      </c>
+      <c r="V99" s="2">
+        <v>46162</v>
+      </c>
+      <c r="W99" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>27</v>
+      </c>
+      <c r="B100" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100" t="s">
+        <v>29</v>
+      </c>
+      <c r="D100" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" t="s">
+        <v>36</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>97.1</v>
+      </c>
+      <c r="N100">
+        <v>155</v>
+      </c>
+      <c r="O100">
+        <v>12</v>
+      </c>
+      <c r="P100">
+        <v>12</v>
+      </c>
+      <c r="R100" t="s">
+        <v>106</v>
+      </c>
+      <c r="S100" s="2">
+        <v>45810</v>
+      </c>
+      <c r="T100" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U100" s="2">
+        <v>46152</v>
+      </c>
+      <c r="V100" s="2">
+        <v>45818</v>
+      </c>
+      <c r="W100" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>27</v>
+      </c>
+      <c r="B101" t="s">
+        <v>42</v>
+      </c>
+      <c r="C101" t="s">
+        <v>46</v>
+      </c>
+      <c r="D101" t="s">
+        <v>43</v>
+      </c>
+      <c r="E101" t="s">
+        <v>36</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>97.1</v>
+      </c>
+      <c r="N101">
+        <v>97.1</v>
+      </c>
+      <c r="R101" t="s">
+        <v>153</v>
+      </c>
+      <c r="S101" s="2">
+        <v>46163</v>
+      </c>
+      <c r="T101" s="2">
+        <v>46163</v>
+      </c>
+      <c r="U101" s="2">
+        <v>46163</v>
+      </c>
+      <c r="V101" s="2">
+        <v>46163</v>
+      </c>
+      <c r="W101" s="2">
+        <v>46163</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>27</v>
+      </c>
+      <c r="B102" t="s">
+        <v>45</v>
+      </c>
+      <c r="C102" t="s">
+        <v>46</v>
+      </c>
+      <c r="D102" t="s">
+        <v>47</v>
+      </c>
+      <c r="E102" t="s">
+        <v>36</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>216</v>
+      </c>
+      <c r="N102">
+        <v>216</v>
+      </c>
+      <c r="O102">
+        <v>17</v>
+      </c>
+      <c r="P102">
+        <v>54</v>
+      </c>
+      <c r="R102" t="s">
+        <v>48</v>
+      </c>
+      <c r="S102" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T102" s="2">
+        <v>46167</v>
+      </c>
+      <c r="U102" s="2">
+        <v>46167</v>
+      </c>
+      <c r="V102" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W102" s="2">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>27</v>
+      </c>
+      <c r="B103" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" t="s">
+        <v>29</v>
+      </c>
+      <c r="D103" t="s">
+        <v>108</v>
+      </c>
+      <c r="E103" t="s">
+        <v>36</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>720</v>
+      </c>
+      <c r="N103">
+        <v>720</v>
+      </c>
+      <c r="O103">
+        <v>5</v>
+      </c>
+      <c r="P103">
+        <v>12</v>
+      </c>
+      <c r="R103" t="s">
+        <v>110</v>
+      </c>
+      <c r="S103" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T103" s="2">
+        <v>46167</v>
+      </c>
+      <c r="U103" s="2">
+        <v>46170</v>
+      </c>
+      <c r="V103" s="2">
+        <v>46052</v>
+      </c>
+      <c r="W103" s="2">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>27</v>
+      </c>
+      <c r="B104" t="s">
+        <v>112</v>
+      </c>
+      <c r="C104" t="s">
+        <v>46</v>
+      </c>
+      <c r="D104" t="s">
+        <v>113</v>
+      </c>
+      <c r="E104" t="s">
+        <v>36</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="M104" s="1">
+        <v>3500</v>
+      </c>
+      <c r="N104" s="1">
+        <v>3500</v>
+      </c>
+      <c r="O104">
+        <v>2</v>
+      </c>
+      <c r="P104">
+        <v>8</v>
+      </c>
+      <c r="R104" t="s">
+        <v>154</v>
+      </c>
+      <c r="S104" s="2">
+        <v>46132</v>
+      </c>
+      <c r="T104" s="2">
+        <v>46167</v>
+      </c>
+      <c r="U104" s="2">
+        <v>46172</v>
+      </c>
+      <c r="V104" s="2">
+        <v>46142</v>
+      </c>
+      <c r="W104" s="2">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>27</v>
+      </c>
+      <c r="B105" t="s">
+        <v>155</v>
+      </c>
+      <c r="E105" t="s">
+        <v>64</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>43.7</v>
+      </c>
+      <c r="N105">
+        <v>43.7</v>
+      </c>
+      <c r="R105" t="s">
+        <v>156</v>
+      </c>
+      <c r="S105" s="2">
+        <v>46172</v>
+      </c>
+      <c r="T105" s="2">
+        <v>46172</v>
+      </c>
+      <c r="U105" s="2">
+        <v>46172</v>
+      </c>
+      <c r="V105" s="2">
+        <v>46172</v>
+      </c>
+      <c r="W105" s="2">
+        <v>46172</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>27</v>
+      </c>
+      <c r="B106" t="s">
+        <v>45</v>
+      </c>
+      <c r="C106" t="s">
+        <v>46</v>
+      </c>
+      <c r="D106" t="s">
+        <v>47</v>
+      </c>
+      <c r="E106" t="s">
+        <v>36</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>144</v>
+      </c>
+      <c r="N106">
+        <v>216</v>
+      </c>
+      <c r="O106">
+        <v>19</v>
+      </c>
+      <c r="P106">
+        <v>54</v>
+      </c>
+      <c r="R106" t="s">
+        <v>48</v>
+      </c>
+      <c r="S106" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T106" s="2">
+        <v>46174</v>
+      </c>
+      <c r="U106" s="2">
+        <v>46181</v>
+      </c>
+      <c r="V106" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W106" s="2">
+        <v>46174</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>27</v>
+      </c>
+      <c r="B107" t="s">
+        <v>49</v>
+      </c>
+      <c r="E107" t="s">
+        <v>36</v>
+      </c>
+      <c r="H107" t="s">
+        <v>51</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>225.6</v>
+      </c>
+      <c r="N107">
+        <v>225.6</v>
+      </c>
+      <c r="P107">
+        <v>1</v>
+      </c>
+      <c r="T107" s="2">
+        <v>46174</v>
+      </c>
+      <c r="U107" s="2">
+        <v>46175</v>
+      </c>
+      <c r="V107" s="2">
+        <v>46125</v>
+      </c>
+      <c r="W107" s="2">
+        <v>46174</v>
+      </c>
+      <c r="X107">
+        <v>253408</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>27</v>
+      </c>
+      <c r="B108" t="s">
+        <v>49</v>
+      </c>
+      <c r="E108" t="s">
+        <v>36</v>
+      </c>
+      <c r="H108" t="s">
+        <v>157</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>292.01</v>
+      </c>
+      <c r="N108">
+        <v>292.01</v>
+      </c>
+      <c r="P108">
+        <v>1</v>
+      </c>
+      <c r="T108" s="2">
+        <v>46174</v>
+      </c>
+      <c r="U108" s="2">
+        <v>46176</v>
+      </c>
+      <c r="V108" s="2">
+        <v>46140</v>
+      </c>
+      <c r="W108" s="2">
+        <v>46174</v>
+      </c>
+      <c r="X108">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>27</v>
+      </c>
+      <c r="B109" t="s">
+        <v>42</v>
+      </c>
+      <c r="C109" t="s">
+        <v>29</v>
+      </c>
+      <c r="D109" t="s">
+        <v>61</v>
+      </c>
+      <c r="E109" t="s">
+        <v>36</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="M109" s="1">
+        <v>2500</v>
+      </c>
+      <c r="N109" s="1">
+        <v>2500</v>
+      </c>
+      <c r="O109">
+        <v>5</v>
+      </c>
+      <c r="P109">
+        <v>12</v>
+      </c>
+      <c r="R109" t="s">
+        <v>62</v>
+      </c>
+      <c r="S109" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T109" s="2">
+        <v>46178</v>
+      </c>
+      <c r="U109" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V109" s="2">
+        <v>46058</v>
+      </c>
+      <c r="W109" s="2">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>27</v>
+      </c>
+      <c r="B110" t="s">
+        <v>45</v>
+      </c>
+      <c r="C110" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" t="s">
+        <v>58</v>
+      </c>
+      <c r="E110" t="s">
+        <v>36</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="M110" s="1">
+        <v>1416.67</v>
+      </c>
+      <c r="N110" s="1">
+        <v>1529.67</v>
+      </c>
+      <c r="O110">
+        <v>3</v>
+      </c>
+      <c r="P110">
+        <v>8</v>
+      </c>
+      <c r="R110" t="s">
+        <v>121</v>
+      </c>
+      <c r="S110" s="2">
+        <v>46116</v>
+      </c>
+      <c r="T110" s="2">
+        <v>46178</v>
+      </c>
+      <c r="U110" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V110" s="2">
+        <v>46117</v>
+      </c>
+      <c r="W110" s="2">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>27</v>
+      </c>
+      <c r="B111" t="s">
+        <v>45</v>
+      </c>
+      <c r="C111" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" t="s">
+        <v>58</v>
+      </c>
+      <c r="E111" t="s">
+        <v>36</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="M111" s="1">
+        <v>1402.17</v>
+      </c>
+      <c r="N111" s="1">
+        <v>1403</v>
+      </c>
+      <c r="O111">
+        <v>2</v>
+      </c>
+      <c r="P111">
+        <v>2</v>
+      </c>
+      <c r="R111" t="s">
+        <v>120</v>
+      </c>
+      <c r="S111" s="2">
+        <v>46141</v>
+      </c>
+      <c r="T111" s="2">
+        <v>46178</v>
+      </c>
+      <c r="U111" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V111" s="2">
+        <v>46147</v>
+      </c>
+      <c r="W111" s="2">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>27</v>
+      </c>
+      <c r="B112" t="s">
+        <v>45</v>
+      </c>
+      <c r="C112" t="s">
+        <v>89</v>
+      </c>
+      <c r="D112" t="s">
+        <v>58</v>
+      </c>
+      <c r="E112" t="s">
+        <v>36</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>905.17</v>
+      </c>
+      <c r="N112">
+        <v>905.17</v>
+      </c>
+      <c r="R112" t="s">
+        <v>158</v>
+      </c>
+      <c r="S112" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T112" s="2">
+        <v>46178</v>
+      </c>
+      <c r="U112" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V112" s="2">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>27</v>
+      </c>
+      <c r="B113" t="s">
+        <v>45</v>
+      </c>
+      <c r="C113" t="s">
+        <v>46</v>
+      </c>
+      <c r="D113" t="s">
+        <v>58</v>
+      </c>
+      <c r="E113" t="s">
+        <v>36</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>783.26</v>
+      </c>
+      <c r="N113">
+        <v>783.26</v>
+      </c>
+      <c r="R113" t="s">
+        <v>159</v>
+      </c>
+      <c r="S113" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T113" s="2">
+        <v>46178</v>
+      </c>
+      <c r="U113" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V113" s="2">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>27</v>
+      </c>
+      <c r="B114" t="s">
+        <v>143</v>
+      </c>
+      <c r="C114" t="s">
+        <v>29</v>
+      </c>
+      <c r="D114" t="s">
+        <v>160</v>
+      </c>
+      <c r="E114" t="s">
+        <v>36</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>50</v>
+      </c>
+      <c r="N114">
+        <v>50</v>
+      </c>
+      <c r="R114" t="s">
+        <v>161</v>
+      </c>
+      <c r="S114" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T114" s="2">
+        <v>46178</v>
+      </c>
+      <c r="U114" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V114" s="2">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>27</v>
+      </c>
+      <c r="B115" t="s">
+        <v>122</v>
+      </c>
+      <c r="C115" t="s">
+        <v>29</v>
+      </c>
+      <c r="D115" t="s">
+        <v>162</v>
+      </c>
+      <c r="E115" t="s">
+        <v>36</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>123.18</v>
+      </c>
+      <c r="N115">
+        <v>123.18</v>
+      </c>
+      <c r="O115">
+        <v>3</v>
+      </c>
+      <c r="P115">
+        <v>3</v>
+      </c>
+      <c r="R115" t="s">
+        <v>163</v>
+      </c>
+      <c r="S115" s="2">
+        <v>46132</v>
+      </c>
+      <c r="T115" s="2">
+        <v>46179</v>
+      </c>
+      <c r="U115" s="2">
+        <v>46183</v>
+      </c>
+      <c r="V115" s="2">
+        <v>46122</v>
+      </c>
+      <c r="W115" s="2">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>27</v>
+      </c>
+      <c r="B116" t="s">
+        <v>164</v>
+      </c>
+      <c r="C116" t="s">
+        <v>133</v>
+      </c>
+      <c r="D116" t="s">
+        <v>134</v>
+      </c>
+      <c r="E116" t="s">
+        <v>36</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>170.68</v>
+      </c>
+      <c r="N116">
+        <v>170.68</v>
+      </c>
+      <c r="R116" t="s">
+        <v>135</v>
+      </c>
+      <c r="S116" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T116" s="2">
+        <v>46179</v>
+      </c>
+      <c r="U116" s="2">
+        <v>46179</v>
+      </c>
+      <c r="V116" s="2">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>27</v>
+      </c>
+      <c r="B117" t="s">
+        <v>107</v>
+      </c>
+      <c r="C117" t="s">
+        <v>46</v>
+      </c>
+      <c r="D117" t="s">
+        <v>84</v>
+      </c>
+      <c r="E117" t="s">
+        <v>36</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>800.9</v>
+      </c>
+      <c r="N117">
+        <v>800.9</v>
+      </c>
+      <c r="R117" t="s">
+        <v>165</v>
+      </c>
+      <c r="S117" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T117" s="2">
+        <v>46179</v>
+      </c>
+      <c r="U117" s="2">
+        <v>46179</v>
+      </c>
+      <c r="V117" s="2">
+        <v>46179</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>27</v>
+      </c>
+      <c r="B118" t="s">
+        <v>45</v>
+      </c>
+      <c r="C118" t="s">
+        <v>29</v>
+      </c>
+      <c r="D118" t="s">
+        <v>47</v>
+      </c>
+      <c r="E118" t="s">
+        <v>36</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>162</v>
+      </c>
+      <c r="N118">
+        <v>162</v>
+      </c>
+      <c r="R118" t="s">
+        <v>166</v>
+      </c>
+      <c r="S118" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T118" s="2">
+        <v>46181</v>
+      </c>
+      <c r="U118" s="2">
+        <v>46181</v>
+      </c>
+      <c r="V118" s="2">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>27</v>
+      </c>
+      <c r="B119" t="s">
+        <v>28</v>
+      </c>
+      <c r="C119" t="s">
+        <v>89</v>
+      </c>
+      <c r="D119" t="s">
+        <v>30</v>
+      </c>
+      <c r="E119" t="s">
+        <v>36</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>620</v>
+      </c>
+      <c r="N119">
+        <v>620</v>
+      </c>
+      <c r="R119" t="s">
+        <v>167</v>
+      </c>
+      <c r="S119" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T119" s="2">
+        <v>46181</v>
+      </c>
+      <c r="U119" s="2">
+        <v>46181</v>
+      </c>
+      <c r="V119" s="2">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>27</v>
+      </c>
+      <c r="B120" t="s">
+        <v>88</v>
+      </c>
+      <c r="C120" t="s">
+        <v>29</v>
+      </c>
+      <c r="D120" t="s">
+        <v>90</v>
+      </c>
+      <c r="E120" t="s">
+        <v>36</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>500</v>
+      </c>
+      <c r="N120">
+        <v>500</v>
+      </c>
+      <c r="R120" t="s">
+        <v>168</v>
+      </c>
+      <c r="S120" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T120" s="2">
+        <v>46182</v>
+      </c>
+      <c r="U120" s="2">
+        <v>46182</v>
+      </c>
+      <c r="V120" s="2">
+        <v>46182</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>27</v>
+      </c>
+      <c r="B121" t="s">
+        <v>45</v>
+      </c>
+      <c r="C121" t="s">
+        <v>29</v>
+      </c>
+      <c r="D121" t="s">
+        <v>47</v>
+      </c>
+      <c r="E121" t="s">
+        <v>36</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>54</v>
+      </c>
+      <c r="N121">
+        <v>54</v>
+      </c>
+      <c r="R121" t="s">
+        <v>169</v>
+      </c>
+      <c r="S121" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T121" s="2">
+        <v>46183</v>
+      </c>
+      <c r="U121" s="2">
+        <v>46183</v>
+      </c>
+      <c r="V121" s="2">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>27</v>
+      </c>
+      <c r="B122" t="s">
+        <v>42</v>
+      </c>
+      <c r="D122" t="s">
+        <v>123</v>
+      </c>
+      <c r="E122" t="s">
+        <v>31</v>
+      </c>
+      <c r="F122" t="s">
+        <v>32</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>7</v>
+      </c>
+      <c r="N122">
+        <v>7</v>
+      </c>
+      <c r="R122" t="s">
+        <v>170</v>
+      </c>
+      <c r="S122" s="2">
+        <v>46184</v>
+      </c>
+      <c r="T122" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U122" s="2">
+        <v>46184</v>
+      </c>
+      <c r="V122" s="2">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>27</v>
+      </c>
+      <c r="B123" t="s">
+        <v>28</v>
+      </c>
+      <c r="D123" t="s">
+        <v>30</v>
+      </c>
+      <c r="E123" t="s">
+        <v>31</v>
+      </c>
+      <c r="F123" t="s">
+        <v>32</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>500</v>
+      </c>
+      <c r="N123">
+        <v>500</v>
+      </c>
+      <c r="R123" t="s">
+        <v>171</v>
+      </c>
+      <c r="S123" s="2">
+        <v>46184</v>
+      </c>
+      <c r="T123" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U123" s="2">
+        <v>46184</v>
+      </c>
+      <c r="V123" s="2">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>27</v>
+      </c>
+      <c r="B124" t="s">
+        <v>42</v>
+      </c>
+      <c r="D124" t="s">
+        <v>123</v>
+      </c>
+      <c r="E124" t="s">
+        <v>31</v>
+      </c>
+      <c r="F124" t="s">
+        <v>32</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>9.9</v>
+      </c>
+      <c r="N124">
+        <v>9.9</v>
+      </c>
+      <c r="R124" t="s">
+        <v>172</v>
+      </c>
+      <c r="S124" s="2">
+        <v>46184</v>
+      </c>
+      <c r="T124" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U124" s="2">
+        <v>46184</v>
+      </c>
+      <c r="V124" s="2">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>27</v>
+      </c>
+      <c r="B125" t="s">
+        <v>49</v>
+      </c>
+      <c r="E125" t="s">
+        <v>36</v>
+      </c>
+      <c r="H125" t="s">
+        <v>51</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>225.6</v>
+      </c>
+      <c r="N125">
+        <v>225.6</v>
+      </c>
+      <c r="P125">
+        <v>1</v>
+      </c>
+      <c r="T125" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U125" s="2">
+        <v>46185</v>
+      </c>
+      <c r="V125" s="2">
+        <v>46125</v>
+      </c>
+      <c r="W125" s="2">
+        <v>46184</v>
+      </c>
+      <c r="X125">
+        <v>253408</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>27</v>
+      </c>
+      <c r="B126" t="s">
+        <v>38</v>
+      </c>
+      <c r="E126" t="s">
+        <v>36</v>
+      </c>
+      <c r="H126" t="s">
+        <v>41</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="N126">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="P126">
+        <v>1</v>
+      </c>
+      <c r="T126" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U126" s="2">
+        <v>46183</v>
+      </c>
+      <c r="V126" s="2">
+        <v>46128</v>
+      </c>
+      <c r="W126" s="2">
+        <v>46184</v>
+      </c>
+      <c r="X126">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>27</v>
+      </c>
+      <c r="B127" t="s">
+        <v>49</v>
+      </c>
+      <c r="E127" t="s">
+        <v>36</v>
+      </c>
+      <c r="H127" t="s">
+        <v>157</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>291.99</v>
+      </c>
+      <c r="N127">
+        <v>291.99</v>
+      </c>
+      <c r="P127">
+        <v>1</v>
+      </c>
+      <c r="T127" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U127" s="2">
+        <v>46183</v>
+      </c>
+      <c r="V127" s="2">
+        <v>46140</v>
+      </c>
+      <c r="W127" s="2">
+        <v>46184</v>
+      </c>
+      <c r="X127">
+        <v>2748</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>27</v>
+      </c>
+      <c r="B128" t="s">
+        <v>140</v>
+      </c>
+      <c r="C128" t="s">
+        <v>133</v>
+      </c>
+      <c r="D128" t="s">
+        <v>173</v>
+      </c>
+      <c r="E128" t="s">
+        <v>36</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>698.25</v>
+      </c>
+      <c r="N128">
+        <v>698.25</v>
+      </c>
+      <c r="R128" t="s">
+        <v>174</v>
+      </c>
+      <c r="S128" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T128" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U128" s="2">
+        <v>46184</v>
+      </c>
+      <c r="V128" s="2">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>27</v>
+      </c>
+      <c r="B129" t="s">
+        <v>38</v>
+      </c>
+      <c r="E129" t="s">
+        <v>36</v>
+      </c>
+      <c r="H129" t="s">
+        <v>41</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>290.75</v>
+      </c>
+      <c r="N129">
+        <v>290.75</v>
+      </c>
+      <c r="P129">
+        <v>1</v>
+      </c>
+      <c r="T129" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U129" s="2">
+        <v>46183</v>
+      </c>
+      <c r="V129" s="2">
+        <v>46163</v>
+      </c>
+      <c r="W129" s="2">
+        <v>46184</v>
+      </c>
+      <c r="X129">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>27</v>
+      </c>
+      <c r="B130" t="s">
+        <v>49</v>
+      </c>
+      <c r="E130" t="s">
+        <v>36</v>
+      </c>
+      <c r="H130" t="s">
+        <v>175</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>209.75</v>
+      </c>
+      <c r="N130">
+        <v>209.75</v>
+      </c>
+      <c r="P130">
+        <v>1</v>
+      </c>
+      <c r="T130" s="2">
+        <v>46184</v>
+      </c>
+      <c r="U130" s="2">
+        <v>46183</v>
+      </c>
+      <c r="V130" s="2">
+        <v>46160</v>
+      </c>
+      <c r="W130" s="2">
+        <v>46184</v>
+      </c>
+      <c r="X130">
+        <v>960006</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>27</v>
+      </c>
+      <c r="B131" t="s">
+        <v>45</v>
+      </c>
+      <c r="C131" t="s">
+        <v>46</v>
+      </c>
+      <c r="D131" t="s">
+        <v>58</v>
+      </c>
+      <c r="E131" t="s">
+        <v>36</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>60</v>
+      </c>
+      <c r="N131">
+        <v>60</v>
+      </c>
+      <c r="R131" t="s">
+        <v>176</v>
+      </c>
+      <c r="S131" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T131" s="2">
+        <v>46186</v>
+      </c>
+      <c r="U131" s="2">
+        <v>46186</v>
+      </c>
+      <c r="V131" s="2">
+        <v>46186</v>
+      </c>
+      <c r="W131" s="2">
+        <v>46186</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>27</v>
+      </c>
+      <c r="B132" t="s">
+        <v>45</v>
+      </c>
+      <c r="C132" t="s">
+        <v>46</v>
+      </c>
+      <c r="D132" t="s">
+        <v>47</v>
+      </c>
+      <c r="E132" t="s">
+        <v>36</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>45</v>
+      </c>
+      <c r="N132">
+        <v>216</v>
+      </c>
+      <c r="O132">
+        <v>20</v>
+      </c>
+      <c r="P132">
+        <v>54</v>
+      </c>
+      <c r="R132" t="s">
+        <v>48</v>
+      </c>
+      <c r="S132" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T132" s="2">
+        <v>46188</v>
+      </c>
+      <c r="U132" s="2">
+        <v>46188</v>
+      </c>
+      <c r="V132" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W132" s="2">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>27</v>
+      </c>
+      <c r="B133" t="s">
+        <v>107</v>
+      </c>
+      <c r="C133" t="s">
+        <v>46</v>
+      </c>
+      <c r="D133" t="s">
+        <v>84</v>
+      </c>
+      <c r="E133" t="s">
+        <v>36</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>50</v>
+      </c>
+      <c r="N133">
+        <v>50</v>
+      </c>
+      <c r="R133" t="s">
+        <v>177</v>
+      </c>
+      <c r="S133" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T133" s="2">
+        <v>46189</v>
+      </c>
+      <c r="U133" s="2">
+        <v>46189</v>
+      </c>
+      <c r="V133" s="2">
+        <v>46189</v>
+      </c>
+      <c r="W133" s="2">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>27</v>
+      </c>
+      <c r="B134" t="s">
+        <v>42</v>
+      </c>
+      <c r="D134" t="s">
+        <v>74</v>
+      </c>
+      <c r="E134" t="s">
+        <v>36</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>22</v>
+      </c>
+      <c r="N134">
+        <v>22</v>
+      </c>
+      <c r="R134" t="s">
+        <v>178</v>
+      </c>
+      <c r="S134" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T134" s="2">
+        <v>46190</v>
+      </c>
+      <c r="U134" s="2">
+        <v>46190</v>
+      </c>
+      <c r="V134" s="2">
+        <v>46190</v>
+      </c>
+      <c r="W134" s="2">
+        <v>46190</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>27</v>
+      </c>
+      <c r="B135" t="s">
+        <v>34</v>
+      </c>
+      <c r="C135" t="s">
+        <v>29</v>
+      </c>
+      <c r="D135" t="s">
+        <v>35</v>
+      </c>
+      <c r="E135" t="s">
+        <v>36</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>31.41</v>
+      </c>
+      <c r="N135">
+        <v>31.41</v>
+      </c>
+      <c r="O135">
+        <v>6</v>
+      </c>
+      <c r="P135">
+        <v>12</v>
+      </c>
+      <c r="R135" t="s">
+        <v>37</v>
+      </c>
+      <c r="S135" s="2">
+        <v>46043</v>
+      </c>
+      <c r="T135" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U135" s="2">
+        <v>46188</v>
+      </c>
+      <c r="V135" s="2">
+        <v>46037</v>
+      </c>
+      <c r="W135" s="2">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>27</v>
+      </c>
+      <c r="B136" t="s">
+        <v>42</v>
+      </c>
+      <c r="C136" t="s">
+        <v>29</v>
+      </c>
+      <c r="D136" t="s">
+        <v>80</v>
+      </c>
+      <c r="E136" t="s">
+        <v>36</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>180</v>
+      </c>
+      <c r="N136">
+        <v>180</v>
+      </c>
+      <c r="O136">
+        <v>6</v>
+      </c>
+      <c r="P136">
+        <v>12</v>
+      </c>
+      <c r="R136" t="s">
+        <v>81</v>
+      </c>
+      <c r="S136" s="2">
+        <v>46043</v>
+      </c>
+      <c r="T136" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U136" s="2">
+        <v>46188</v>
+      </c>
+      <c r="V136" s="2">
+        <v>46037</v>
+      </c>
+      <c r="W136" s="2">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>27</v>
+      </c>
+      <c r="B137" t="s">
+        <v>45</v>
+      </c>
+      <c r="C137" t="s">
+        <v>29</v>
+      </c>
+      <c r="D137" t="s">
+        <v>84</v>
+      </c>
+      <c r="E137" t="s">
+        <v>36</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>769.49</v>
+      </c>
+      <c r="N137">
+        <v>499.78</v>
+      </c>
+      <c r="O137">
+        <v>6</v>
+      </c>
+      <c r="P137">
+        <v>12</v>
+      </c>
+      <c r="R137" t="s">
+        <v>115</v>
+      </c>
+      <c r="S137" s="2">
+        <v>46053</v>
+      </c>
+      <c r="T137" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U137" s="2">
+        <v>46193</v>
+      </c>
+      <c r="V137" s="2">
+        <v>46042</v>
+      </c>
+      <c r="W137" s="2">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>27</v>
+      </c>
+      <c r="B138" t="s">
+        <v>38</v>
+      </c>
+      <c r="E138" t="s">
+        <v>36</v>
+      </c>
+      <c r="H138" t="s">
+        <v>41</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="N138">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="P138">
+        <v>1</v>
+      </c>
+      <c r="T138" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U138" s="2">
+        <v>46193</v>
+      </c>
+      <c r="V138" s="2">
+        <v>46128</v>
+      </c>
+      <c r="W138" s="2">
+        <v>46192</v>
+      </c>
+      <c r="X138">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>27</v>
+      </c>
+      <c r="B139" t="s">
+        <v>45</v>
+      </c>
+      <c r="C139" t="s">
+        <v>29</v>
+      </c>
+      <c r="D139" t="s">
+        <v>138</v>
+      </c>
+      <c r="E139" t="s">
+        <v>36</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>753.93</v>
+      </c>
+      <c r="N139">
+        <v>648.04</v>
+      </c>
+      <c r="O139">
+        <v>2</v>
+      </c>
+      <c r="P139">
+        <v>8</v>
+      </c>
+      <c r="R139" t="s">
+        <v>139</v>
+      </c>
+      <c r="S139" s="2">
+        <v>46146</v>
+      </c>
+      <c r="T139" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U139" s="2">
+        <v>46193</v>
+      </c>
+      <c r="V139" s="2">
+        <v>46162</v>
+      </c>
+      <c r="W139" s="2">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>27</v>
+      </c>
+      <c r="B140" t="s">
+        <v>103</v>
+      </c>
+      <c r="C140" t="s">
+        <v>29</v>
+      </c>
+      <c r="D140" t="s">
+        <v>104</v>
+      </c>
+      <c r="E140" t="s">
+        <v>36</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="M140" s="1">
+        <v>2811.82</v>
+      </c>
+      <c r="N140" s="1">
+        <v>2811.82</v>
+      </c>
+      <c r="S140" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T140" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U140" s="2">
+        <v>46192</v>
+      </c>
+      <c r="V140" s="2">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>27</v>
+      </c>
+      <c r="B141" t="s">
+        <v>38</v>
+      </c>
+      <c r="E141" t="s">
+        <v>36</v>
+      </c>
+      <c r="H141" t="s">
+        <v>41</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>290.76</v>
+      </c>
+      <c r="N141">
+        <v>290.76</v>
+      </c>
+      <c r="P141">
+        <v>1</v>
+      </c>
+      <c r="T141" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U141" s="2">
+        <v>46193</v>
+      </c>
+      <c r="V141" s="2">
+        <v>46163</v>
+      </c>
+      <c r="W141" s="2">
+        <v>46192</v>
+      </c>
+      <c r="X141">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>27</v>
+      </c>
+      <c r="B142" t="s">
+        <v>38</v>
+      </c>
+      <c r="E142" t="s">
+        <v>36</v>
+      </c>
+      <c r="H142" t="s">
+        <v>41</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>290.76</v>
+      </c>
+      <c r="N142">
+        <v>290.76</v>
+      </c>
+      <c r="P142">
+        <v>1</v>
+      </c>
+      <c r="T142" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U142" s="2">
+        <v>46203</v>
+      </c>
+      <c r="V142" s="2">
+        <v>46163</v>
+      </c>
+      <c r="W142" s="2">
+        <v>46192</v>
+      </c>
+      <c r="X142">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>27</v>
+      </c>
+      <c r="B143" t="s">
+        <v>49</v>
+      </c>
+      <c r="E143" t="s">
+        <v>36</v>
+      </c>
+      <c r="H143" t="s">
+        <v>175</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>209.75</v>
+      </c>
+      <c r="N143">
+        <v>209.75</v>
+      </c>
+      <c r="P143">
+        <v>1</v>
+      </c>
+      <c r="T143" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U143" s="2">
+        <v>46190</v>
+      </c>
+      <c r="V143" s="2">
+        <v>46160</v>
+      </c>
+      <c r="W143" s="2">
+        <v>46192</v>
+      </c>
+      <c r="X143">
+        <v>960006</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>27</v>
+      </c>
+      <c r="B144" t="s">
+        <v>49</v>
+      </c>
+      <c r="E144" t="s">
+        <v>36</v>
+      </c>
+      <c r="H144" t="s">
+        <v>175</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>209.75</v>
+      </c>
+      <c r="N144">
+        <v>209.75</v>
+      </c>
+      <c r="P144">
+        <v>1</v>
+      </c>
+      <c r="T144" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U144" s="2">
+        <v>46197</v>
+      </c>
+      <c r="V144" s="2">
+        <v>46160</v>
+      </c>
+      <c r="W144" s="2">
+        <v>46192</v>
+      </c>
+      <c r="X144">
+        <v>960006</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>27</v>
+      </c>
+      <c r="B145" t="s">
+        <v>122</v>
+      </c>
+      <c r="C145" t="s">
+        <v>89</v>
+      </c>
+      <c r="D145" t="s">
+        <v>101</v>
+      </c>
+      <c r="E145" t="s">
+        <v>36</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>182.87</v>
+      </c>
+      <c r="N145">
+        <v>182.87</v>
+      </c>
+      <c r="R145" t="s">
+        <v>179</v>
+      </c>
+      <c r="S145" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T145" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U145" s="2">
+        <v>46192</v>
+      </c>
+      <c r="V145" s="2">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>27</v>
+      </c>
+      <c r="B146" t="s">
+        <v>103</v>
+      </c>
+      <c r="C146" t="s">
+        <v>89</v>
+      </c>
+      <c r="D146" t="s">
+        <v>104</v>
+      </c>
+      <c r="E146" t="s">
+        <v>36</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>20.59</v>
+      </c>
+      <c r="N146">
+        <v>20.59</v>
+      </c>
+      <c r="R146" t="s">
+        <v>180</v>
+      </c>
+      <c r="S146" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T146" s="2">
+        <v>46192</v>
+      </c>
+      <c r="U146" s="2">
+        <v>46192</v>
+      </c>
+      <c r="V146" s="2">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>27</v>
+      </c>
+      <c r="B147" t="s">
+        <v>143</v>
+      </c>
+      <c r="C147" t="s">
+        <v>46</v>
+      </c>
+      <c r="D147" t="s">
+        <v>84</v>
+      </c>
+      <c r="E147" t="s">
+        <v>36</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>275</v>
+      </c>
+      <c r="N147">
+        <v>275</v>
+      </c>
+      <c r="S147" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T147" s="2">
+        <v>46193</v>
+      </c>
+      <c r="U147" s="2">
+        <v>46193</v>
+      </c>
+      <c r="V147" s="2">
+        <v>46193</v>
+      </c>
+      <c r="W147" s="2">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>27</v>
+      </c>
+      <c r="B148" t="s">
+        <v>45</v>
+      </c>
+      <c r="C148" t="s">
+        <v>46</v>
+      </c>
+      <c r="D148" t="s">
+        <v>47</v>
+      </c>
+      <c r="E148" t="s">
+        <v>36</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>207</v>
+      </c>
+      <c r="N148">
+        <v>216</v>
+      </c>
+      <c r="O148">
+        <v>21</v>
+      </c>
+      <c r="P148">
+        <v>54</v>
+      </c>
+      <c r="R148" t="s">
+        <v>48</v>
+      </c>
+      <c r="S148" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T148" s="2">
+        <v>46195</v>
+      </c>
+      <c r="U148" s="2">
+        <v>46195</v>
+      </c>
+      <c r="V148" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W148" s="2">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>27</v>
+      </c>
+      <c r="B149" t="s">
+        <v>107</v>
+      </c>
+      <c r="C149" t="s">
+        <v>46</v>
+      </c>
+      <c r="D149" t="s">
+        <v>84</v>
+      </c>
+      <c r="E149" t="s">
+        <v>36</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>50</v>
+      </c>
+      <c r="N149">
+        <v>50</v>
+      </c>
+      <c r="R149" t="s">
+        <v>181</v>
+      </c>
+      <c r="S149" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T149" s="2">
+        <v>46195</v>
+      </c>
+      <c r="U149" s="2">
+        <v>46195</v>
+      </c>
+      <c r="V149" s="2">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>27</v>
+      </c>
+      <c r="B150" t="s">
+        <v>45</v>
+      </c>
+      <c r="C150" t="s">
+        <v>89</v>
+      </c>
+      <c r="D150" t="s">
+        <v>58</v>
+      </c>
+      <c r="E150" t="s">
+        <v>36</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>200</v>
+      </c>
+      <c r="N150">
+        <v>200</v>
+      </c>
+      <c r="R150" t="s">
+        <v>182</v>
+      </c>
+      <c r="S150" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T150" s="2">
+        <v>46197</v>
+      </c>
+      <c r="U150" s="2">
+        <v>46197</v>
+      </c>
+      <c r="V150" s="2">
+        <v>46197</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>27</v>
+      </c>
+      <c r="B151" t="s">
+        <v>42</v>
+      </c>
+      <c r="C151" t="s">
+        <v>29</v>
+      </c>
+      <c r="D151" t="s">
+        <v>43</v>
+      </c>
+      <c r="E151" t="s">
+        <v>36</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>585.82000000000005</v>
+      </c>
+      <c r="N151">
+        <v>458.46</v>
+      </c>
+      <c r="O151">
+        <v>6</v>
+      </c>
+      <c r="P151">
+        <v>12</v>
+      </c>
+      <c r="R151" t="s">
+        <v>79</v>
+      </c>
+      <c r="S151" s="2">
+        <v>46038</v>
+      </c>
+      <c r="T151" s="2">
+        <v>46198</v>
+      </c>
+      <c r="U151" s="2">
+        <v>46174</v>
+      </c>
+      <c r="V151" s="2">
+        <v>46023</v>
+      </c>
+      <c r="W151" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>27</v>
+      </c>
+      <c r="B152" t="s">
+        <v>45</v>
+      </c>
+      <c r="C152" t="s">
+        <v>46</v>
+      </c>
+      <c r="D152" t="s">
+        <v>47</v>
+      </c>
+      <c r="E152" t="s">
+        <v>36</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>144</v>
+      </c>
+      <c r="N152">
+        <v>216</v>
+      </c>
+      <c r="O152">
+        <v>18</v>
+      </c>
+      <c r="P152">
+        <v>54</v>
+      </c>
+      <c r="R152" t="s">
+        <v>48</v>
+      </c>
+      <c r="S152" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T152" s="2">
+        <v>46198</v>
+      </c>
+      <c r="U152" s="2">
+        <v>46174</v>
+      </c>
+      <c r="V152" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W152" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>27</v>
+      </c>
+      <c r="B153" t="s">
+        <v>34</v>
+      </c>
+      <c r="C153" t="s">
+        <v>29</v>
+      </c>
+      <c r="D153" t="s">
+        <v>71</v>
+      </c>
+      <c r="E153" t="s">
+        <v>36</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>533.92999999999995</v>
+      </c>
+      <c r="N153">
+        <v>533.92999999999995</v>
+      </c>
+      <c r="O153">
+        <v>4</v>
+      </c>
+      <c r="P153">
+        <v>10</v>
+      </c>
+      <c r="R153" t="s">
+        <v>72</v>
+      </c>
+      <c r="S153" s="2">
+        <v>46111</v>
+      </c>
+      <c r="T153" s="2">
+        <v>46198</v>
+      </c>
+      <c r="U153" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V153" s="2">
+        <v>46086</v>
+      </c>
+      <c r="W153" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>27</v>
+      </c>
+      <c r="B154" t="s">
+        <v>49</v>
+      </c>
+      <c r="E154" t="s">
+        <v>36</v>
+      </c>
+      <c r="H154" t="s">
+        <v>118</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>251.51</v>
+      </c>
+      <c r="N154">
+        <v>251.51</v>
+      </c>
+      <c r="P154">
+        <v>1</v>
+      </c>
+      <c r="T154" s="2">
+        <v>46198</v>
+      </c>
+      <c r="U154" s="2">
+        <v>46179</v>
+      </c>
+      <c r="V154" s="2">
+        <v>46100</v>
+      </c>
+      <c r="W154" s="2">
+        <v>46198</v>
+      </c>
+      <c r="X154">
+        <v>777612</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>27</v>
+      </c>
+      <c r="B155" t="s">
+        <v>42</v>
+      </c>
+      <c r="C155" t="s">
+        <v>89</v>
+      </c>
+      <c r="D155" t="s">
+        <v>43</v>
+      </c>
+      <c r="E155" t="s">
+        <v>36</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>585.82000000000005</v>
+      </c>
+      <c r="N155">
+        <v>585.82000000000005</v>
+      </c>
+      <c r="R155" t="s">
+        <v>183</v>
+      </c>
+      <c r="S155" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T155" s="2">
+        <v>46198</v>
+      </c>
+      <c r="U155" s="2">
+        <v>46198</v>
+      </c>
+      <c r="V155" s="2">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>27</v>
+      </c>
+      <c r="B156" t="s">
+        <v>42</v>
+      </c>
+      <c r="C156" t="s">
+        <v>29</v>
+      </c>
+      <c r="D156" t="s">
+        <v>43</v>
+      </c>
+      <c r="E156" t="s">
+        <v>36</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>56.46</v>
+      </c>
+      <c r="N156">
+        <v>70</v>
+      </c>
+      <c r="O156">
+        <v>6</v>
+      </c>
+      <c r="P156">
+        <v>10</v>
+      </c>
+      <c r="R156" t="s">
+        <v>44</v>
+      </c>
+      <c r="S156" s="2">
+        <v>46032</v>
+      </c>
+      <c r="T156" s="2">
+        <v>46200</v>
+      </c>
+      <c r="U156" s="2">
+        <v>46188</v>
+      </c>
+      <c r="V156" s="2">
+        <v>46037</v>
+      </c>
+      <c r="W156" s="2">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>27</v>
+      </c>
+      <c r="B157" t="s">
+        <v>49</v>
+      </c>
+      <c r="C157" t="s">
+        <v>89</v>
+      </c>
+      <c r="D157" t="s">
+        <v>98</v>
+      </c>
+      <c r="E157" t="s">
+        <v>36</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>619.46</v>
+      </c>
+      <c r="N157">
+        <v>619.46</v>
+      </c>
+      <c r="S157" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T157" s="2">
+        <v>46200</v>
+      </c>
+      <c r="U157" s="2">
+        <v>46200</v>
+      </c>
+      <c r="V157" s="2">
+        <v>46200</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>27</v>
+      </c>
+      <c r="B158" t="s">
+        <v>45</v>
+      </c>
+      <c r="C158" t="s">
+        <v>46</v>
+      </c>
+      <c r="D158" t="s">
+        <v>47</v>
+      </c>
+      <c r="E158" t="s">
+        <v>36</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>108</v>
+      </c>
+      <c r="N158">
+        <v>216</v>
+      </c>
+      <c r="O158">
+        <v>22</v>
+      </c>
+      <c r="P158">
+        <v>54</v>
+      </c>
+      <c r="R158" t="s">
+        <v>48</v>
+      </c>
+      <c r="S158" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T158" s="2">
+        <v>46202</v>
+      </c>
+      <c r="U158" s="2">
+        <v>46202</v>
+      </c>
+      <c r="V158" s="2">
+        <v>46055</v>
+      </c>
+      <c r="W158" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>27</v>
+      </c>
+      <c r="B159" t="s">
+        <v>28</v>
+      </c>
+      <c r="C159" t="s">
+        <v>133</v>
+      </c>
+      <c r="D159" t="s">
+        <v>30</v>
+      </c>
+      <c r="E159" t="s">
+        <v>36</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>620</v>
+      </c>
+      <c r="N159">
+        <v>620</v>
+      </c>
+      <c r="R159" t="s">
+        <v>184</v>
+      </c>
+      <c r="S159" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T159" s="2">
+        <v>46202</v>
+      </c>
+      <c r="U159" s="2">
+        <v>46202</v>
+      </c>
+      <c r="V159" s="2">
+        <v>46202</v>
+      </c>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>27</v>
+      </c>
+      <c r="B160" t="s">
+        <v>107</v>
+      </c>
+      <c r="C160" t="s">
+        <v>29</v>
+      </c>
+      <c r="D160" t="s">
+        <v>108</v>
+      </c>
+      <c r="E160" t="s">
+        <v>36</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="M160" s="1">
+        <v>1000</v>
+      </c>
+      <c r="N160" s="1">
+        <v>1000</v>
+      </c>
+      <c r="O160">
+        <v>6</v>
+      </c>
+      <c r="P160">
+        <v>12</v>
+      </c>
+      <c r="R160" t="s">
+        <v>109</v>
+      </c>
+      <c r="S160" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T160" s="2">
+        <v>46203</v>
+      </c>
+      <c r="U160" s="2">
+        <v>46201</v>
+      </c>
+      <c r="V160" s="2">
+        <v>46052</v>
+      </c>
+      <c r="W160" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>27</v>
+      </c>
+      <c r="B161" t="s">
+        <v>107</v>
+      </c>
+      <c r="C161" t="s">
+        <v>29</v>
+      </c>
+      <c r="D161" t="s">
+        <v>108</v>
+      </c>
+      <c r="E161" t="s">
+        <v>36</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>720</v>
+      </c>
+      <c r="N161">
+        <v>720</v>
+      </c>
+      <c r="O161">
+        <v>6</v>
+      </c>
+      <c r="P161">
+        <v>12</v>
+      </c>
+      <c r="R161" t="s">
+        <v>110</v>
+      </c>
+      <c r="S161" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T161" s="2">
+        <v>46203</v>
+      </c>
+      <c r="U161" s="2">
+        <v>46201</v>
+      </c>
+      <c r="V161" s="2">
+        <v>46052</v>
+      </c>
+      <c r="W161" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>27</v>
+      </c>
+      <c r="B162" t="s">
+        <v>107</v>
+      </c>
+      <c r="C162" t="s">
+        <v>29</v>
+      </c>
+      <c r="D162" t="s">
+        <v>108</v>
+      </c>
+      <c r="E162" t="s">
+        <v>36</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>550</v>
+      </c>
+      <c r="N162">
+        <v>550</v>
+      </c>
+      <c r="O162">
+        <v>6</v>
+      </c>
+      <c r="P162">
+        <v>12</v>
+      </c>
+      <c r="S162" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T162" s="2">
+        <v>46203</v>
+      </c>
+      <c r="U162" s="2">
+        <v>46201</v>
+      </c>
+      <c r="V162" s="2">
+        <v>46052</v>
+      </c>
+      <c r="W162" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>27</v>
+      </c>
+      <c r="B163" t="s">
+        <v>112</v>
+      </c>
+      <c r="C163" t="s">
+        <v>46</v>
+      </c>
+      <c r="D163" t="s">
+        <v>113</v>
+      </c>
+      <c r="E163" t="s">
+        <v>36</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="M163" s="1">
+        <v>3500</v>
+      </c>
+      <c r="N163" s="1">
+        <v>3500</v>
+      </c>
+      <c r="O163">
+        <v>3</v>
+      </c>
+      <c r="P163">
+        <v>8</v>
+      </c>
+      <c r="R163" t="s">
+        <v>154</v>
+      </c>
+      <c r="S163" s="2">
+        <v>46132</v>
+      </c>
+      <c r="T163" s="2">
+        <v>46203</v>
+      </c>
+      <c r="U163" s="2">
+        <v>46203</v>
+      </c>
+      <c r="V163" s="2">
+        <v>46142</v>
+      </c>
+      <c r="W163" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>27</v>
+      </c>
+      <c r="B164" t="s">
+        <v>164</v>
+      </c>
+      <c r="C164" t="s">
+        <v>133</v>
+      </c>
+      <c r="D164" t="s">
+        <v>134</v>
+      </c>
+      <c r="E164" t="s">
+        <v>36</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>90</v>
+      </c>
+      <c r="N164">
+        <v>90</v>
+      </c>
+      <c r="R164" t="s">
+        <v>185</v>
+      </c>
+      <c r="S164" s="2">
+        <v>46209</v>
+      </c>
+      <c r="T164" s="2">
+        <v>46203</v>
+      </c>
+      <c r="U164" s="2">
+        <v>46203</v>
+      </c>
+      <c r="V164" s="2">
+        <v>46203</v>
+      </c>
+      <c r="W164" s="2">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>27</v>
+      </c>
+      <c r="B165" t="s">
+        <v>42</v>
+      </c>
+      <c r="C165" t="s">
+        <v>29</v>
+      </c>
+      <c r="D165" t="s">
+        <v>43</v>
+      </c>
+      <c r="E165" t="s">
+        <v>36</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>458.46</v>
+      </c>
+      <c r="N165">
+        <v>458.46</v>
+      </c>
+      <c r="O165">
+        <v>7</v>
+      </c>
+      <c r="P165">
+        <v>12</v>
+      </c>
+      <c r="R165" t="s">
+        <v>79</v>
+      </c>
+      <c r="S165" s="2">
+        <v>46038</v>
+      </c>
+      <c r="T165" s="2">
+        <v>46204</v>
+      </c>
+      <c r="U165" s="2">
+        <v>46204</v>
+      </c>
+      <c r="V165" s="2">
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>27</v>
+      </c>
+      <c r="B166" t="s">
+        <v>45</v>
+      </c>
+      <c r="D166" t="s">
+        <v>74</v>
+      </c>
+      <c r="E166" t="s">
+        <v>31</v>
+      </c>
+      <c r="F166" t="s">
+        <v>32</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <v>14</v>
+      </c>
+      <c r="N166">
+        <v>14</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>75</v>
+      </c>
+      <c r="R166" t="s">
+        <v>186</v>
+      </c>
+      <c r="S166" s="2">
+        <v>46204</v>
+      </c>
+      <c r="T166" s="2">
+        <v>46204</v>
+      </c>
+      <c r="U166" s="2">
+        <v>46204</v>
+      </c>
+      <c r="V166" s="2">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>27</v>
+      </c>
+      <c r="B167" t="s">
+        <v>45</v>
+      </c>
+      <c r="C167" t="s">
+        <v>29</v>
+      </c>
+      <c r="D167" t="s">
+        <v>58</v>
+      </c>
+      <c r="E167" t="s">
+        <v>36</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="M167" s="1">
+        <v>1313.07</v>
+      </c>
+      <c r="N167" s="1">
+        <v>1313.07</v>
+      </c>
+      <c r="O167">
+        <v>9</v>
+      </c>
+      <c r="P167">
+        <v>12</v>
+      </c>
+      <c r="R167" t="s">
+        <v>60</v>
+      </c>
+      <c r="S167" s="2">
+        <v>45931</v>
+      </c>
+      <c r="T167" s="2">
+        <v>46208</v>
+      </c>
+      <c r="U167" s="2">
+        <v>46208</v>
+      </c>
+      <c r="V167" s="2">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>27</v>
+      </c>
+      <c r="B168" t="s">
+        <v>42</v>
+      </c>
+      <c r="C168" t="s">
+        <v>29</v>
+      </c>
+      <c r="D168" t="s">
+        <v>61</v>
+      </c>
+      <c r="E168" t="s">
+        <v>36</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="M168" s="1">
+        <v>2500</v>
+      </c>
+      <c r="N168" s="1">
+        <v>2500</v>
+      </c>
+      <c r="O168">
+        <v>6</v>
+      </c>
+      <c r="P168">
+        <v>12</v>
+      </c>
+      <c r="R168" t="s">
+        <v>62</v>
+      </c>
+      <c r="S168" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T168" s="2">
+        <v>46208</v>
+      </c>
+      <c r="U168" s="2">
+        <v>46208</v>
+      </c>
+      <c r="V168" s="2">
+        <v>46058</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>27</v>
+      </c>
+      <c r="B169" t="s">
+        <v>187</v>
+      </c>
+      <c r="C169" t="s">
+        <v>46</v>
+      </c>
+      <c r="D169" t="s">
+        <v>67</v>
+      </c>
+      <c r="E169" t="s">
+        <v>36</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>799</v>
+      </c>
+      <c r="N169">
+        <v>799</v>
+      </c>
+      <c r="O169">
+        <v>8</v>
+      </c>
+      <c r="P169">
+        <v>10</v>
+      </c>
+      <c r="R169" t="s">
+        <v>68</v>
+      </c>
+      <c r="S169" s="2">
+        <v>46052</v>
+      </c>
+      <c r="T169" s="2">
+        <v>46208</v>
+      </c>
+      <c r="U169" s="2">
+        <v>46208</v>
+      </c>
+      <c r="V169" s="2">
+        <v>45996</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>27</v>
+      </c>
+      <c r="E170" t="s">
+        <v>40</v>
+      </c>
+      <c r="H170" t="s">
+        <v>77</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>328.54</v>
+      </c>
+      <c r="N170">
+        <v>328.54</v>
+      </c>
+      <c r="P170">
+        <v>1</v>
+      </c>
+      <c r="T170" s="2">
+        <v>46208</v>
+      </c>
+      <c r="U170" s="2">
+        <v>46208</v>
+      </c>
+      <c r="V170" s="2">
+        <v>46052</v>
+      </c>
+      <c r="X170">
+        <v>60852</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>27</v>
+      </c>
+      <c r="B171" t="s">
+        <v>34</v>
+      </c>
+      <c r="C171" t="s">
+        <v>29</v>
+      </c>
+      <c r="D171" t="s">
+        <v>71</v>
+      </c>
+      <c r="E171" t="s">
+        <v>36</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>533.92999999999995</v>
+      </c>
+      <c r="N171">
+        <v>533.92999999999995</v>
+      </c>
+      <c r="O171">
+        <v>5</v>
+      </c>
+      <c r="P171">
+        <v>10</v>
+      </c>
+      <c r="R171" t="s">
+        <v>72</v>
+      </c>
+      <c r="S171" s="2">
+        <v>46111</v>
+      </c>
+      <c r="T171" s="2">
+        <v>46208</v>
+      </c>
+      <c r="U171" s="2">
+        <v>46208</v>
+      </c>
+      <c r="V171" s="2">
+        <v>46086</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>27</v>
+      </c>
+      <c r="B172" t="s">
+        <v>45</v>
+      </c>
+      <c r="C172" t="s">
+        <v>46</v>
+      </c>
+      <c r="D172" t="s">
+        <v>58</v>
+      </c>
+      <c r="E172" t="s">
+        <v>36</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="M172" s="1">
+        <v>1529.67</v>
+      </c>
+      <c r="N172" s="1">
+        <v>1529.67</v>
+      </c>
+      <c r="O172">
+        <v>4</v>
+      </c>
+      <c r="P172">
+        <v>8</v>
+      </c>
+      <c r="R172" t="s">
+        <v>121</v>
+      </c>
+      <c r="S172" s="2">
+        <v>46116</v>
+      </c>
+      <c r="T172" s="2">
+        <v>46208</v>
+      </c>
+      <c r="U172" s="2">
+        <v>46208</v>
+      </c>
+      <c r="V172" s="2">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>27</v>
+      </c>
+      <c r="B173" t="s">
+        <v>34</v>
+      </c>
+      <c r="C173" t="s">
+        <v>29</v>
+      </c>
+      <c r="D173" t="s">
+        <v>65</v>
+      </c>
+      <c r="E173" t="s">
+        <v>36</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>199.92</v>
+      </c>
+      <c r="N173">
+        <v>199.92</v>
+      </c>
+      <c r="O173">
+        <v>4</v>
+      </c>
+      <c r="P173">
+        <v>10</v>
+      </c>
+      <c r="R173" t="s">
+        <v>130</v>
+      </c>
+      <c r="S173" s="2">
+        <v>46116</v>
+      </c>
+      <c r="T173" s="2">
+        <v>46208</v>
+      </c>
+      <c r="U173" s="2">
+        <v>46208</v>
+      </c>
+      <c r="V173" s="2">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>27</v>
+      </c>
+      <c r="B174" t="s">
+        <v>126</v>
+      </c>
+      <c r="C174" t="s">
+        <v>29</v>
+      </c>
+      <c r="D174" t="s">
+        <v>63</v>
+      </c>
+      <c r="E174" t="s">
+        <v>36</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>15.35</v>
+      </c>
+      <c r="N174">
+        <v>15.35</v>
+      </c>
+      <c r="O174">
+        <v>3</v>
+      </c>
+      <c r="P174">
+        <v>6</v>
+      </c>
+      <c r="R174" t="s">
+        <v>127</v>
+      </c>
+      <c r="S174" s="2">
+        <v>46141</v>
+      </c>
+      <c r="T174" s="2">
+        <v>46208</v>
+      </c>
+      <c r="U174" s="2">
+        <v>46208</v>
+      </c>
+      <c r="V174" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>27</v>
+      </c>
+      <c r="B175" t="s">
+        <v>45</v>
+      </c>
+      <c r="C175" t="s">
+        <v>46</v>
+      </c>
+      <c r="D175" t="s">
+        <v>47</v>
+      </c>
+      <c r="E175" t="s">
+        <v>36</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <v>216</v>
+      </c>
+      <c r="N175">
+        <v>216</v>
+      </c>
+      <c r="O175">
+        <v>23</v>
+      </c>
+      <c r="P175">
+        <v>54</v>
+      </c>
+      <c r="R175" t="s">
+        <v>48</v>
+      </c>
+      <c r="S175" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T175" s="2">
+        <v>46209</v>
+      </c>
+      <c r="U175" s="2">
+        <v>46209</v>
+      </c>
+      <c r="V175" s="2">
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>27</v>
+      </c>
+      <c r="B176" t="s">
+        <v>187</v>
+      </c>
+      <c r="C176" t="s">
+        <v>46</v>
+      </c>
+      <c r="D176" t="s">
+        <v>67</v>
+      </c>
+      <c r="E176" t="s">
+        <v>36</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <v>799</v>
+      </c>
+      <c r="N176">
+        <v>799</v>
+      </c>
+      <c r="O176">
+        <v>7</v>
+      </c>
+      <c r="P176">
+        <v>10</v>
+      </c>
+      <c r="R176" t="s">
+        <v>68</v>
+      </c>
+      <c r="S176" s="2">
+        <v>46052</v>
+      </c>
+      <c r="T176" s="2">
+        <v>46209</v>
+      </c>
+      <c r="U176" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V176" s="2">
+        <v>45996</v>
+      </c>
+      <c r="W176" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>27</v>
+      </c>
+      <c r="E177" t="s">
+        <v>40</v>
+      </c>
+      <c r="H177" t="s">
+        <v>77</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>328.54</v>
+      </c>
+      <c r="N177">
+        <v>328.54</v>
+      </c>
+      <c r="P177">
+        <v>1</v>
+      </c>
+      <c r="T177" s="2">
+        <v>46209</v>
+      </c>
+      <c r="U177" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V177" s="2">
+        <v>46052</v>
+      </c>
+      <c r="W177" s="2">
+        <v>46209</v>
+      </c>
+      <c r="X177">
+        <v>60852</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>27</v>
+      </c>
+      <c r="B178" t="s">
+        <v>34</v>
+      </c>
+      <c r="C178" t="s">
+        <v>29</v>
+      </c>
+      <c r="D178" t="s">
+        <v>65</v>
+      </c>
+      <c r="E178" t="s">
+        <v>36</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>199.92</v>
+      </c>
+      <c r="N178">
+        <v>199.92</v>
+      </c>
+      <c r="O178">
+        <v>3</v>
+      </c>
+      <c r="P178">
+        <v>10</v>
+      </c>
+      <c r="R178" t="s">
+        <v>130</v>
+      </c>
+      <c r="S178" s="2">
+        <v>46116</v>
+      </c>
+      <c r="T178" s="2">
+        <v>46209</v>
+      </c>
+      <c r="U178" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V178" s="2">
+        <v>46117</v>
+      </c>
+      <c r="W178" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>27</v>
+      </c>
+      <c r="B179" t="s">
+        <v>126</v>
+      </c>
+      <c r="C179" t="s">
+        <v>29</v>
+      </c>
+      <c r="D179" t="s">
+        <v>63</v>
+      </c>
+      <c r="E179" t="s">
+        <v>36</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>15.35</v>
+      </c>
+      <c r="N179">
+        <v>15.35</v>
+      </c>
+      <c r="O179">
+        <v>2</v>
+      </c>
+      <c r="P179">
+        <v>6</v>
+      </c>
+      <c r="R179" t="s">
+        <v>127</v>
+      </c>
+      <c r="S179" s="2">
+        <v>46141</v>
+      </c>
+      <c r="T179" s="2">
+        <v>46209</v>
+      </c>
+      <c r="U179" s="2">
+        <v>46178</v>
+      </c>
+      <c r="V179" s="2">
+        <v>46147</v>
+      </c>
+      <c r="W179" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>27</v>
+      </c>
+      <c r="B180" t="s">
+        <v>42</v>
+      </c>
+      <c r="D180" t="s">
+        <v>43</v>
+      </c>
+      <c r="E180" t="s">
+        <v>31</v>
+      </c>
+      <c r="F180" t="s">
+        <v>32</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>300</v>
+      </c>
+      <c r="N180">
+        <v>300</v>
+      </c>
+      <c r="R180" t="s">
+        <v>188</v>
+      </c>
+      <c r="S180" s="2">
+        <v>46211</v>
+      </c>
+      <c r="T180" s="2">
+        <v>46211</v>
+      </c>
+      <c r="U180" s="2">
+        <v>46211</v>
+      </c>
+      <c r="V180" s="2">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>27</v>
+      </c>
+      <c r="B181" t="s">
+        <v>42</v>
+      </c>
+      <c r="D181" t="s">
+        <v>39</v>
+      </c>
+      <c r="E181" t="s">
+        <v>31</v>
+      </c>
+      <c r="F181" t="s">
+        <v>32</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <v>386</v>
+      </c>
+      <c r="N181">
+        <v>386</v>
+      </c>
+      <c r="R181" t="s">
+        <v>150</v>
+      </c>
+      <c r="S181" s="2">
+        <v>46212</v>
+      </c>
+      <c r="T181" s="2">
+        <v>46212</v>
+      </c>
+      <c r="U181" s="2">
+        <v>46212</v>
+      </c>
+      <c r="V181" s="2">
+        <v>46212</v>
+      </c>
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>27</v>
+      </c>
+      <c r="B182" t="s">
+        <v>45</v>
+      </c>
+      <c r="C182" t="s">
+        <v>29</v>
+      </c>
+      <c r="D182" t="s">
+        <v>144</v>
+      </c>
+      <c r="E182" t="s">
+        <v>36</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>780</v>
+      </c>
+      <c r="N182">
+        <v>780</v>
+      </c>
+      <c r="O182">
+        <v>6</v>
+      </c>
+      <c r="P182">
+        <v>12</v>
+      </c>
+      <c r="R182" t="s">
+        <v>145</v>
+      </c>
+      <c r="S182" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T182" s="2">
+        <v>46213</v>
+      </c>
+      <c r="U182" s="2">
+        <v>46213</v>
+      </c>
+      <c r="V182" s="2">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>27</v>
+      </c>
+      <c r="B183" t="s">
+        <v>45</v>
+      </c>
+      <c r="C183" t="s">
+        <v>46</v>
+      </c>
+      <c r="D183" t="s">
+        <v>173</v>
+      </c>
+      <c r="E183" t="s">
+        <v>36</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>500</v>
+      </c>
+      <c r="N183">
+        <v>500</v>
+      </c>
+      <c r="O183">
+        <v>7</v>
+      </c>
+      <c r="P183">
+        <v>12</v>
+      </c>
+      <c r="R183" t="s">
+        <v>189</v>
+      </c>
+      <c r="S183" s="2">
+        <v>46053</v>
+      </c>
+      <c r="T183" s="2">
+        <v>46213</v>
+      </c>
+      <c r="U183" s="2">
+        <v>46213</v>
+      </c>
+      <c r="V183" s="2">
+        <v>46032</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>27</v>
+      </c>
+      <c r="E184" t="s">
+        <v>36</v>
+      </c>
+      <c r="H184" t="s">
+        <v>41</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>290.76</v>
+      </c>
+      <c r="N184">
+        <v>290.76</v>
+      </c>
+      <c r="P184">
+        <v>1</v>
+      </c>
+      <c r="T184" s="2">
+        <v>46213</v>
+      </c>
+      <c r="U184" s="2">
+        <v>46213</v>
+      </c>
+      <c r="V184" s="2">
+        <v>46163</v>
+      </c>
+      <c r="X184">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>27</v>
+      </c>
+      <c r="B185" t="s">
+        <v>45</v>
+      </c>
+      <c r="C185" t="s">
+        <v>46</v>
+      </c>
+      <c r="D185" t="s">
+        <v>47</v>
+      </c>
+      <c r="E185" t="s">
+        <v>36</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>216</v>
+      </c>
+      <c r="N185">
+        <v>216</v>
+      </c>
+      <c r="O185">
+        <v>24</v>
+      </c>
+      <c r="P185">
+        <v>54</v>
+      </c>
+      <c r="R185" t="s">
+        <v>48</v>
+      </c>
+      <c r="S185" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T185" s="2">
+        <v>46216</v>
+      </c>
+      <c r="U185" s="2">
+        <v>46216</v>
+      </c>
+      <c r="V185" s="2">
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>27</v>
+      </c>
+      <c r="B186" t="s">
+        <v>42</v>
+      </c>
+      <c r="D186" t="s">
+        <v>30</v>
+      </c>
+      <c r="E186" t="s">
+        <v>31</v>
+      </c>
+      <c r="F186" t="s">
+        <v>32</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <v>100</v>
+      </c>
+      <c r="N186">
+        <v>100</v>
+      </c>
+      <c r="R186" t="s">
+        <v>97</v>
+      </c>
+      <c r="S186" s="2">
+        <v>46216</v>
+      </c>
+      <c r="T186" s="2">
+        <v>46216</v>
+      </c>
+      <c r="U186" s="2">
+        <v>46216</v>
+      </c>
+      <c r="V186" s="2">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>27</v>
+      </c>
+      <c r="B187" t="s">
+        <v>45</v>
+      </c>
+      <c r="D187" t="s">
+        <v>74</v>
+      </c>
+      <c r="E187" t="s">
+        <v>31</v>
+      </c>
+      <c r="F187" t="s">
+        <v>32</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <v>24</v>
+      </c>
+      <c r="N187">
+        <v>24</v>
+      </c>
+      <c r="Q187" t="s">
+        <v>75</v>
+      </c>
+      <c r="R187" t="s">
+        <v>190</v>
+      </c>
+      <c r="S187" s="2">
+        <v>46216</v>
+      </c>
+      <c r="T187" s="2">
+        <v>46216</v>
+      </c>
+      <c r="U187" s="2">
+        <v>46216</v>
+      </c>
+      <c r="V187" s="2">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>27</v>
+      </c>
+      <c r="B188" t="s">
+        <v>42</v>
+      </c>
+      <c r="C188" t="s">
+        <v>29</v>
+      </c>
+      <c r="D188" t="s">
+        <v>43</v>
+      </c>
+      <c r="E188" t="s">
+        <v>36</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <v>70</v>
+      </c>
+      <c r="N188">
+        <v>70</v>
+      </c>
+      <c r="O188">
+        <v>7</v>
+      </c>
+      <c r="P188">
+        <v>10</v>
+      </c>
+      <c r="R188" t="s">
+        <v>44</v>
+      </c>
+      <c r="S188" s="2">
+        <v>46032</v>
+      </c>
+      <c r="T188" s="2">
+        <v>46218</v>
+      </c>
+      <c r="U188" s="2">
+        <v>46218</v>
+      </c>
+      <c r="V188" s="2">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>27</v>
+      </c>
+      <c r="B189" t="s">
+        <v>191</v>
+      </c>
+      <c r="C189" t="s">
+        <v>29</v>
+      </c>
+      <c r="D189" t="s">
+        <v>35</v>
+      </c>
+      <c r="E189" t="s">
+        <v>36</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="M189">
+        <v>31.41</v>
+      </c>
+      <c r="N189">
+        <v>31.41</v>
+      </c>
+      <c r="O189">
+        <v>7</v>
+      </c>
+      <c r="P189">
+        <v>12</v>
+      </c>
+      <c r="R189" t="s">
+        <v>37</v>
+      </c>
+      <c r="S189" s="2">
+        <v>46043</v>
+      </c>
+      <c r="T189" s="2">
+        <v>46218</v>
+      </c>
+      <c r="U189" s="2">
+        <v>46218</v>
+      </c>
+      <c r="V189" s="2">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>27</v>
+      </c>
+      <c r="B190" t="s">
+        <v>42</v>
+      </c>
+      <c r="C190" t="s">
+        <v>29</v>
+      </c>
+      <c r="D190" t="s">
+        <v>80</v>
+      </c>
+      <c r="E190" t="s">
+        <v>36</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <v>180</v>
+      </c>
+      <c r="N190">
+        <v>180</v>
+      </c>
+      <c r="O190">
+        <v>7</v>
+      </c>
+      <c r="P190">
+        <v>12</v>
+      </c>
+      <c r="R190" t="s">
+        <v>81</v>
+      </c>
+      <c r="S190" s="2">
+        <v>46043</v>
+      </c>
+      <c r="T190" s="2">
+        <v>46218</v>
+      </c>
+      <c r="U190" s="2">
+        <v>46218</v>
+      </c>
+      <c r="V190" s="2">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>27</v>
+      </c>
+      <c r="E191" t="s">
+        <v>36</v>
+      </c>
+      <c r="H191" t="s">
+        <v>175</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <v>224.83</v>
+      </c>
+      <c r="N191">
+        <v>224.83</v>
+      </c>
+      <c r="P191">
+        <v>1</v>
+      </c>
+      <c r="T191" s="2">
+        <v>46218</v>
+      </c>
+      <c r="U191" s="2">
+        <v>46218</v>
+      </c>
+      <c r="V191" s="2">
+        <v>46186</v>
+      </c>
+      <c r="X191">
+        <v>964382</v>
+      </c>
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>27</v>
+      </c>
+      <c r="B192" t="s">
+        <v>45</v>
+      </c>
+      <c r="C192" t="s">
+        <v>46</v>
+      </c>
+      <c r="D192" t="s">
+        <v>47</v>
+      </c>
+      <c r="E192" t="s">
+        <v>36</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <v>216</v>
+      </c>
+      <c r="N192">
+        <v>216</v>
+      </c>
+      <c r="O192">
+        <v>2</v>
+      </c>
+      <c r="P192">
+        <v>54</v>
+      </c>
+      <c r="S192" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T192" s="2">
+        <v>46222</v>
+      </c>
+      <c r="U192" s="2">
+        <v>46222</v>
+      </c>
+      <c r="V192" s="2">
+        <v>46041</v>
+      </c>
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>27</v>
+      </c>
+      <c r="B193" t="s">
+        <v>45</v>
+      </c>
+      <c r="C193" t="s">
+        <v>46</v>
+      </c>
+      <c r="D193" t="s">
+        <v>47</v>
+      </c>
+      <c r="E193" t="s">
+        <v>36</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <v>216</v>
+      </c>
+      <c r="N193">
+        <v>216</v>
+      </c>
+      <c r="O193">
+        <v>25</v>
+      </c>
+      <c r="P193">
+        <v>54</v>
+      </c>
+      <c r="R193" t="s">
+        <v>48</v>
+      </c>
+      <c r="S193" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T193" s="2">
+        <v>46223</v>
+      </c>
+      <c r="U193" s="2">
+        <v>46223</v>
+      </c>
+      <c r="V193" s="2">
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>27</v>
+      </c>
+      <c r="B194" t="s">
+        <v>45</v>
+      </c>
+      <c r="C194" t="s">
+        <v>29</v>
+      </c>
+      <c r="D194" t="s">
+        <v>84</v>
+      </c>
+      <c r="E194" t="s">
+        <v>36</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <v>499.78</v>
+      </c>
+      <c r="N194">
+        <v>499.78</v>
+      </c>
+      <c r="O194">
+        <v>7</v>
+      </c>
+      <c r="P194">
+        <v>12</v>
+      </c>
+      <c r="R194" t="s">
+        <v>115</v>
+      </c>
+      <c r="S194" s="2">
+        <v>46053</v>
+      </c>
+      <c r="T194" s="2">
+        <v>46223</v>
+      </c>
+      <c r="U194" s="2">
+        <v>46223</v>
+      </c>
+      <c r="V194" s="2">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>27</v>
+      </c>
+      <c r="B195" t="s">
+        <v>103</v>
+      </c>
+      <c r="C195" t="s">
+        <v>29</v>
+      </c>
+      <c r="D195" t="s">
+        <v>104</v>
+      </c>
+      <c r="E195" t="s">
+        <v>36</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="M195" s="1">
+        <v>3157.93</v>
+      </c>
+      <c r="N195" s="1">
+        <v>3157.93</v>
+      </c>
+      <c r="O195">
+        <v>4</v>
+      </c>
+      <c r="P195">
+        <v>10</v>
+      </c>
+      <c r="R195" t="s">
+        <v>149</v>
+      </c>
+      <c r="S195" s="2">
+        <v>46132</v>
+      </c>
+      <c r="T195" s="2">
+        <v>46223</v>
+      </c>
+      <c r="U195" s="2">
+        <v>46223</v>
+      </c>
+      <c r="V195" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>27</v>
+      </c>
+      <c r="B196" t="s">
+        <v>45</v>
+      </c>
+      <c r="C196" t="s">
+        <v>29</v>
+      </c>
+      <c r="D196" t="s">
+        <v>136</v>
+      </c>
+      <c r="E196" t="s">
+        <v>36</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <v>697.21</v>
+      </c>
+      <c r="N196">
+        <v>697.21</v>
+      </c>
+      <c r="O196">
+        <v>3</v>
+      </c>
+      <c r="P196">
+        <v>8</v>
+      </c>
+      <c r="R196" t="s">
+        <v>137</v>
+      </c>
+      <c r="S196" s="2">
+        <v>46146</v>
+      </c>
+      <c r="T196" s="2">
+        <v>46223</v>
+      </c>
+      <c r="U196" s="2">
+        <v>46223</v>
+      </c>
+      <c r="V196" s="2">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>27</v>
+      </c>
+      <c r="B197" t="s">
+        <v>45</v>
+      </c>
+      <c r="C197" t="s">
+        <v>29</v>
+      </c>
+      <c r="D197" t="s">
+        <v>138</v>
+      </c>
+      <c r="E197" t="s">
+        <v>36</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <v>648.04</v>
+      </c>
+      <c r="N197">
+        <v>648.04</v>
+      </c>
+      <c r="O197">
+        <v>3</v>
+      </c>
+      <c r="P197">
+        <v>8</v>
+      </c>
+      <c r="R197" t="s">
+        <v>139</v>
+      </c>
+      <c r="S197" s="2">
+        <v>46146</v>
+      </c>
+      <c r="T197" s="2">
+        <v>46223</v>
+      </c>
+      <c r="U197" s="2">
+        <v>46223</v>
+      </c>
+      <c r="V197" s="2">
+        <v>46162</v>
+      </c>
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>27</v>
+      </c>
+      <c r="E198" t="s">
+        <v>36</v>
+      </c>
+      <c r="H198" t="s">
+        <v>41</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <v>290.76</v>
+      </c>
+      <c r="N198">
+        <v>290.76</v>
+      </c>
+      <c r="P198">
+        <v>1</v>
+      </c>
+      <c r="T198" s="2">
+        <v>46223</v>
+      </c>
+      <c r="U198" s="2">
+        <v>46223</v>
+      </c>
+      <c r="V198" s="2">
+        <v>46163</v>
+      </c>
+      <c r="X198">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>27</v>
+      </c>
+      <c r="E199" t="s">
+        <v>36</v>
+      </c>
+      <c r="H199" t="s">
+        <v>175</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <v>224.83</v>
+      </c>
+      <c r="N199">
+        <v>224.83</v>
+      </c>
+      <c r="P199">
+        <v>1</v>
+      </c>
+      <c r="T199" s="2">
+        <v>46225</v>
+      </c>
+      <c r="U199" s="2">
+        <v>46225</v>
+      </c>
+      <c r="V199" s="2">
+        <v>46186</v>
+      </c>
+      <c r="X199">
+        <v>964382</v>
+      </c>
+    </row>
+    <row r="200" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>27</v>
+      </c>
+      <c r="B200" t="s">
+        <v>45</v>
+      </c>
+      <c r="C200" t="s">
+        <v>46</v>
+      </c>
+      <c r="D200" t="s">
+        <v>47</v>
+      </c>
+      <c r="E200" t="s">
+        <v>36</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <v>216</v>
+      </c>
+      <c r="N200">
+        <v>216</v>
+      </c>
+      <c r="O200">
+        <v>26</v>
+      </c>
+      <c r="P200">
+        <v>54</v>
+      </c>
+      <c r="R200" t="s">
+        <v>48</v>
+      </c>
+      <c r="S200" s="2">
+        <v>46048</v>
+      </c>
+      <c r="T200" s="2">
+        <v>46230</v>
+      </c>
+      <c r="U200" s="2">
+        <v>46230</v>
+      </c>
+      <c r="V200" s="2">
+        <v>46055</v>
+      </c>
+    </row>
+    <row r="201" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>27</v>
+      </c>
+      <c r="B201" t="s">
+        <v>192</v>
+      </c>
+      <c r="C201" t="s">
+        <v>29</v>
+      </c>
+      <c r="D201" t="s">
+        <v>108</v>
+      </c>
+      <c r="E201" t="s">
+        <v>36</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="M201" s="1">
+        <v>1000</v>
+      </c>
+      <c r="N201" s="1">
+        <v>1000</v>
+      </c>
+      <c r="O201">
+        <v>7</v>
+      </c>
+      <c r="P201">
+        <v>12</v>
+      </c>
+      <c r="R201" t="s">
+        <v>109</v>
+      </c>
+      <c r="S201" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T201" s="2">
+        <v>46231</v>
+      </c>
+      <c r="U201" s="2">
+        <v>46231</v>
+      </c>
+      <c r="V201" s="2">
+        <v>46052</v>
+      </c>
+    </row>
+    <row r="202" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>27</v>
+      </c>
+      <c r="B202" t="s">
+        <v>193</v>
+      </c>
+      <c r="C202" t="s">
+        <v>29</v>
+      </c>
+      <c r="D202" t="s">
+        <v>108</v>
+      </c>
+      <c r="E202" t="s">
+        <v>36</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="M202">
+        <v>720</v>
+      </c>
+      <c r="N202">
+        <v>720</v>
+      </c>
+      <c r="O202">
+        <v>7</v>
+      </c>
+      <c r="P202">
+        <v>12</v>
+      </c>
+      <c r="R202" t="s">
+        <v>110</v>
+      </c>
+      <c r="S202" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T202" s="2">
+        <v>46231</v>
+      </c>
+      <c r="U202" s="2">
+        <v>46231</v>
+      </c>
+      <c r="V202" s="2">
+        <v>46052</v>
+      </c>
+    </row>
+    <row r="203" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>27</v>
+      </c>
+      <c r="B203" t="s">
+        <v>193</v>
+      </c>
+      <c r="C203" t="s">
+        <v>29</v>
+      </c>
+      <c r="D203" t="s">
+        <v>108</v>
+      </c>
+      <c r="E203" t="s">
+        <v>36</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="M203">
+        <v>550</v>
+      </c>
+      <c r="N203">
+        <v>550</v>
+      </c>
+      <c r="O203">
+        <v>7</v>
+      </c>
+      <c r="P203">
+        <v>12</v>
+      </c>
+      <c r="S203" s="2">
+        <v>46037</v>
+      </c>
+      <c r="T203" s="2">
+        <v>46231</v>
+      </c>
+      <c r="U203" s="2">
+        <v>46231</v>
+      </c>
+      <c r="V203" s="2">
+        <v>46052</v>
+      </c>
+    </row>
+    <row r="204" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>27</v>
+      </c>
+      <c r="B204" t="s">
+        <v>45</v>
+      </c>
+      <c r="C204" t="s">
+        <v>46</v>
+      </c>
+      <c r="D204" t="s">
+        <v>113</v>
+      </c>
+      <c r="E204" t="s">
+        <v>36</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="M204" s="1">
+        <v>3500</v>
+      </c>
+      <c r="N204" s="1">
+        <v>3500</v>
+      </c>
+      <c r="O204">
+        <v>4</v>
+      </c>
+      <c r="P204">
+        <v>8</v>
+      </c>
+      <c r="R204" t="s">
+        <v>154</v>
+      </c>
+      <c r="S204" s="2">
+        <v>46132</v>
+      </c>
+      <c r="T204" s="2">
+        <v>46233</v>
+      </c>
+      <c r="U204" s="2">
+        <v>46233</v>
+      </c>
+      <c r="V204" s="2">
+        <v>46142</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{57368c21-b8cf-42cf-bd0b-43ecd4bc62ae}" enabled="0" method="" siteId="{57368c21-b8cf-42cf-bd0b-43ecd4bc62ae}" removed="1"/>
+</clbl:labelList>
 </file>